--- a/RIGEL/会社概要・資料/事業計画書・融資/日本政策金融公庫_創業計画書.xlsx
+++ b/RIGEL/会社概要・資料/事業計画書・融資/日本政策金融公庫_創業計画書.xlsx
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="191">
   <si>
     <t xml:space="preserve">創　業　計　画　書</t>
   </si>
@@ -170,6 +170,9 @@
     <t xml:space="preserve">お名前</t>
   </si>
   <si>
+    <t xml:space="preserve">佐藤 貴久</t>
+  </si>
+  <si>
     <t xml:space="preserve">☆　この書類に代えて、お客さまご自身が作成された計画書をご提出いただいても結構です。</t>
   </si>
   <si>
@@ -230,7 +233,7 @@
     <t xml:space="preserve">年間返済額</t>
   </si>
   <si>
-    <t xml:space="preserve">退職予定（前職の勤務先・役職・担当業務は要本人追記）</t>
+    <t xml:space="preserve">退職予定（株式会社サンエイテック・課長）</t>
   </si>
   <si>
     <t xml:space="preserve">事業</t>
@@ -266,10 +269,10 @@
     <t xml:space="preserve">FA設備／RTS事業を開始予定</t>
   </si>
   <si>
-    <t xml:space="preserve">【要追記】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FA設備・ロボットシステム分野の実務経歴、担当案件、保有技能</t>
+    <t xml:space="preserve">－</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社サンエイテックにて課長職。FA設備・ロボットシステム分野の3D機械設計に約20年間従事。</t>
   </si>
   <si>
     <t xml:space="preserve">８　必要な資金と調達方法</t>
@@ -345,7 +348,7 @@
     <t xml:space="preserve">取得資格</t>
   </si>
   <si>
-    <t xml:space="preserve">特になし</t>
+    <t xml:space="preserve">○特になし</t>
   </si>
   <si>
     <t xml:space="preserve">有</t>
@@ -702,7 +705,8 @@
   <si>
     <t xml:space="preserve">最大の論点は運転資金確保。FA設備は設計〜検収〜入金まで3〜6か月を要し、先行部材費が大きい。
 初期投資848万円、運転資金2,035万円、合計2,883万円を資金計画の基準値とした。
-なお、代表者経歴、自己資金額、取引先実名、見積書、必要許認可の有無は提出前に本人確認が必要。</t>
+なお、代表者経歴、自己資金額、取引先実名、見積書、必要許認可の有無は提出前に本人確認が必要。
+自己資金300万円、日本政策金融公庫からの借入2,583万円（想定利率2.5%）で資金計画を構成。</t>
   </si>
   <si>
     <t xml:space="preserve">日支払</t>
@@ -1424,7 +1428,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1448,17 +1452,13 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="312">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1674,7 +1674,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1718,7 +1718,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1762,7 +1762,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1806,7 +1806,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="44" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1818,7 +1818,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="27" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1854,7 +1854,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="49" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1886,7 +1886,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="49" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1894,7 +1894,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1942,7 +1942,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="49" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1990,7 +1990,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="59" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2010,7 +2010,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="33" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2062,7 +2062,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="49" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2098,7 +2098,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="59" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2134,11 +2134,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="19" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2158,11 +2158,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="56" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="56" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2170,7 +2170,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="49" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2258,7 +2258,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="63" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="63" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2266,7 +2266,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="63" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2274,11 +2274,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2326,7 +2326,7 @@
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="28" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2358,15 +2358,11 @@
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="33" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="7" fillId="5" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="19" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2374,7 +2370,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2382,7 +2378,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="22" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2390,7 +2386,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="18" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2406,7 +2402,7 @@
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="33" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2414,10 +2410,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2570,7 +2562,7 @@
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="38" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2578,10 +2570,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -2618,7 +2606,7 @@
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2626,11 +2614,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2719,14 +2703,13 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Comma [0]" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -3195,7 +3178,9 @@
       <c r="S4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="18"/>
+      <c r="T4" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="U4" s="18"/>
       <c r="V4" s="16"/>
       <c r="W4" s="16"/>
@@ -3216,7 +3201,7 @@
       <c r="AL4" s="16"/>
       <c r="AM4" s="16"/>
       <c r="AO4" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP4" s="20"/>
       <c r="AQ4" s="18"/>
@@ -3262,10 +3247,10 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BU6" s="2"/>
       <c r="BV6" s="2"/>
@@ -3314,11 +3299,11 @@
       <c r="AL7" s="25"/>
       <c r="AM7" s="25"/>
       <c r="AO7" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP7" s="26"/>
       <c r="AQ7" s="27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR7" s="27"/>
       <c r="AS7" s="27"/>
@@ -3337,11 +3322,11 @@
       <c r="BF7" s="28"/>
       <c r="BG7" s="28"/>
       <c r="BH7" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BI7" s="26"/>
       <c r="BJ7" s="27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BK7" s="27"/>
       <c r="BL7" s="27"/>
@@ -3362,7 +3347,7 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
@@ -3404,7 +3389,7 @@
       <c r="AO8" s="26"/>
       <c r="AP8" s="26"/>
       <c r="AQ8" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR8" s="31"/>
       <c r="AS8" s="31"/>
@@ -3425,7 +3410,7 @@
       <c r="BH8" s="26"/>
       <c r="BI8" s="26"/>
       <c r="BJ8" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BK8" s="31"/>
       <c r="BL8" s="31"/>
@@ -3446,7 +3431,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -3488,7 +3473,7 @@
       <c r="AO9" s="26"/>
       <c r="AP9" s="26"/>
       <c r="AQ9" s="31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR9" s="31"/>
       <c r="AS9" s="31"/>
@@ -3509,7 +3494,7 @@
       <c r="BH9" s="26"/>
       <c r="BI9" s="26"/>
       <c r="BJ9" s="31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BK9" s="31"/>
       <c r="BL9" s="31"/>
@@ -3530,7 +3515,7 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
@@ -3572,7 +3557,7 @@
       <c r="AO10" s="26"/>
       <c r="AP10" s="26"/>
       <c r="AQ10" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR10" s="35"/>
       <c r="AS10" s="35"/>
@@ -3593,7 +3578,7 @@
       <c r="BH10" s="26"/>
       <c r="BI10" s="26"/>
       <c r="BJ10" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BK10" s="35"/>
       <c r="BL10" s="35"/>
@@ -3614,13 +3599,13 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
       <c r="AM11" s="39"/>
       <c r="AO11" s="24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BU11" s="2"/>
       <c r="BV11" s="2"/>
@@ -3631,7 +3616,7 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
@@ -3639,7 +3624,7 @@
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
       <c r="H12" s="41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" s="41"/>
       <c r="J12" s="41"/>
@@ -3673,7 +3658,7 @@
       <c r="AL12" s="41"/>
       <c r="AM12" s="41"/>
       <c r="AO12" s="42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP12" s="42"/>
       <c r="AQ12" s="42"/>
@@ -3684,7 +3669,7 @@
       <c r="AV12" s="42"/>
       <c r="AW12" s="42"/>
       <c r="AX12" s="43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY12" s="43"/>
       <c r="AZ12" s="43"/>
@@ -3705,14 +3690,14 @@
       <c r="BO12" s="44"/>
       <c r="BP12" s="45"/>
       <c r="BQ12" s="46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BR12" s="46"/>
       <c r="BS12" s="46"/>
       <c r="BT12" s="46"/>
       <c r="BU12" s="46"/>
       <c r="BV12" s="47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW12" s="47"/>
       <c r="BX12" s="47"/>
@@ -3729,7 +3714,7 @@
       <c r="F13" s="48"/>
       <c r="G13" s="48"/>
       <c r="H13" s="49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="49"/>
       <c r="J13" s="49"/>
@@ -3774,31 +3759,31 @@
       <c r="AX13" s="51"/>
       <c r="AY13" s="52"/>
       <c r="AZ13" s="53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BA13" s="53"/>
       <c r="BB13" s="52"/>
       <c r="BC13" s="53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD13" s="53"/>
       <c r="BE13" s="52"/>
       <c r="BF13" s="53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG13" s="52"/>
       <c r="BH13" s="53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BI13" s="53"/>
       <c r="BJ13" s="52"/>
       <c r="BK13" s="54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BL13" s="53"/>
       <c r="BM13" s="52"/>
       <c r="BN13" s="54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BO13" s="55"/>
       <c r="BP13" s="56"/>
@@ -3806,20 +3791,20 @@
       <c r="BR13" s="57"/>
       <c r="BS13" s="57"/>
       <c r="BT13" s="58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BU13" s="58"/>
       <c r="BV13" s="57"/>
       <c r="BW13" s="57"/>
       <c r="BX13" s="57"/>
       <c r="BY13" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ13" s="59"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -3827,7 +3812,7 @@
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
       <c r="H14" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
@@ -3872,31 +3857,31 @@
       <c r="AX14" s="62"/>
       <c r="AY14" s="63"/>
       <c r="AZ14" s="64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BA14" s="64"/>
       <c r="BB14" s="63"/>
       <c r="BC14" s="64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD14" s="64"/>
       <c r="BE14" s="63"/>
       <c r="BF14" s="64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG14" s="63"/>
       <c r="BH14" s="64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BI14" s="64"/>
       <c r="BJ14" s="63"/>
       <c r="BK14" s="65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BL14" s="64"/>
       <c r="BM14" s="63"/>
       <c r="BN14" s="65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BO14" s="66"/>
       <c r="BP14" s="67"/>
@@ -3904,20 +3889,20 @@
       <c r="BR14" s="68"/>
       <c r="BS14" s="68"/>
       <c r="BT14" s="69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BU14" s="69"/>
       <c r="BV14" s="68"/>
       <c r="BW14" s="68"/>
       <c r="BX14" s="68"/>
       <c r="BY14" s="70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ14" s="70"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="71"/>
       <c r="D15" s="71"/>
@@ -3925,7 +3910,7 @@
       <c r="F15" s="71"/>
       <c r="G15" s="71"/>
       <c r="H15" s="30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
@@ -3970,31 +3955,31 @@
       <c r="AX15" s="73"/>
       <c r="AY15" s="74"/>
       <c r="AZ15" s="75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BA15" s="75"/>
       <c r="BB15" s="74"/>
       <c r="BC15" s="75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD15" s="75"/>
       <c r="BE15" s="74"/>
       <c r="BF15" s="75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG15" s="74"/>
       <c r="BH15" s="75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BI15" s="75"/>
       <c r="BJ15" s="74"/>
       <c r="BK15" s="76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BL15" s="75"/>
       <c r="BM15" s="74"/>
       <c r="BN15" s="76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BO15" s="77"/>
       <c r="BP15" s="78"/>
@@ -4002,20 +3987,20 @@
       <c r="BR15" s="79"/>
       <c r="BS15" s="79"/>
       <c r="BT15" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BU15" s="80"/>
       <c r="BV15" s="79"/>
       <c r="BW15" s="79"/>
       <c r="BX15" s="79"/>
       <c r="BY15" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ15" s="81"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="82"/>
       <c r="D16" s="82"/>
@@ -4023,7 +4008,7 @@
       <c r="F16" s="82"/>
       <c r="G16" s="82"/>
       <c r="H16" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
@@ -4057,7 +4042,7 @@
       <c r="AL16" s="30"/>
       <c r="AM16" s="30"/>
       <c r="AO16" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4100,7 +4085,7 @@
       <c r="AL17" s="33"/>
       <c r="AM17" s="33"/>
       <c r="AO17" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AP17" s="42"/>
       <c r="AQ17" s="42"/>
@@ -4112,21 +4097,21 @@
       <c r="AW17" s="42"/>
       <c r="AX17" s="42"/>
       <c r="AY17" s="46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AZ17" s="46"/>
       <c r="BA17" s="46"/>
       <c r="BB17" s="46"/>
       <c r="BC17" s="46"/>
       <c r="BD17" s="47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BE17" s="47"/>
       <c r="BF17" s="47"/>
       <c r="BG17" s="47"/>
       <c r="BH17" s="47"/>
       <c r="BI17" s="40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BJ17" s="40"/>
       <c r="BK17" s="40"/>
@@ -4141,7 +4126,7 @@
       <c r="BT17" s="40"/>
       <c r="BU17" s="40"/>
       <c r="BV17" s="47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BW17" s="47"/>
       <c r="BX17" s="47"/>
@@ -4188,10 +4173,10 @@
       <c r="AL18" s="37"/>
       <c r="AM18" s="37"/>
       <c r="AO18" s="85" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AP18" s="86" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AQ18" s="86"/>
       <c r="AR18" s="86"/>
@@ -4213,11 +4198,11 @@
       <c r="BE18" s="88"/>
       <c r="BF18" s="88"/>
       <c r="BG18" s="89" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BH18" s="89"/>
       <c r="BI18" s="90" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BJ18" s="90"/>
       <c r="BK18" s="90"/>
@@ -4232,18 +4217,18 @@
       <c r="BT18" s="90"/>
       <c r="BU18" s="90"/>
       <c r="BV18" s="91" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="BW18" s="91"/>
       <c r="BX18" s="91"/>
       <c r="BY18" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ18" s="59"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="92"/>
       <c r="D19" s="92"/>
@@ -4252,7 +4237,7 @@
       <c r="G19" s="92"/>
       <c r="H19" s="93"/>
       <c r="I19" s="94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J19" s="95"/>
       <c r="K19" s="95"/>
@@ -4286,7 +4271,7 @@
       <c r="AM19" s="97"/>
       <c r="AO19" s="85"/>
       <c r="AP19" s="98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AQ19" s="98"/>
       <c r="AR19" s="98"/>
@@ -4297,7 +4282,7 @@
       <c r="AW19" s="98"/>
       <c r="AX19" s="98"/>
       <c r="AY19" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ19" s="99"/>
       <c r="BA19" s="99"/>
@@ -4338,12 +4323,12 @@
       <c r="G20" s="92"/>
       <c r="H20" s="101"/>
       <c r="I20" s="102" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA20" s="103"/>
       <c r="AB20" s="103"/>
       <c r="AC20" s="104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD20" s="104"/>
       <c r="AE20" s="104"/>
@@ -4355,11 +4340,11 @@
       <c r="AK20" s="105"/>
       <c r="AL20" s="105"/>
       <c r="AM20" s="106" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO20" s="85"/>
       <c r="AP20" s="107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AQ20" s="107"/>
       <c r="AR20" s="107"/>
@@ -4370,7 +4355,7 @@
       <c r="AW20" s="107"/>
       <c r="AX20" s="107"/>
       <c r="AY20" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ20" s="99"/>
       <c r="BA20" s="99"/>
@@ -4384,7 +4369,7 @@
       <c r="BG20" s="108"/>
       <c r="BH20" s="108"/>
       <c r="BI20" s="109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BJ20" s="109"/>
       <c r="BK20" s="109"/>
@@ -4404,7 +4389,7 @@
       <c r="BW20" s="110"/>
       <c r="BX20" s="110"/>
       <c r="BY20" s="111" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ20" s="111"/>
     </row>
@@ -4417,7 +4402,7 @@
       <c r="G21" s="92"/>
       <c r="H21" s="112"/>
       <c r="I21" s="113" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J21" s="39"/>
       <c r="K21" s="39"/>
@@ -4439,7 +4424,7 @@
       <c r="AA21" s="115"/>
       <c r="AB21" s="116"/>
       <c r="AC21" s="113" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD21" s="113"/>
       <c r="AE21" s="113"/>
@@ -4452,14 +4437,14 @@
       </c>
       <c r="AK21" s="119"/>
       <c r="AL21" s="118" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM21" s="120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO21" s="85"/>
       <c r="AP21" s="107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AQ21" s="107"/>
       <c r="AR21" s="107"/>
@@ -4470,7 +4455,7 @@
       <c r="AW21" s="107"/>
       <c r="AX21" s="107"/>
       <c r="AY21" s="99" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AZ21" s="99"/>
       <c r="BA21" s="99"/>
@@ -4484,7 +4469,7 @@
       <c r="BG21" s="108"/>
       <c r="BH21" s="108"/>
       <c r="BI21" s="121" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BJ21" s="121"/>
       <c r="BK21" s="121"/>
@@ -4506,7 +4491,7 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
@@ -4515,17 +4500,17 @@
       <c r="G22" s="26"/>
       <c r="H22" s="123"/>
       <c r="I22" s="124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J22" s="124"/>
       <c r="K22" s="124"/>
       <c r="L22" s="125"/>
       <c r="M22" s="124"/>
       <c r="N22" s="124" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O22" s="126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P22" s="127"/>
       <c r="Q22" s="127"/>
@@ -4542,7 +4527,7 @@
       <c r="AB22" s="127"/>
       <c r="AC22" s="127"/>
       <c r="AD22" s="128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE22" s="128"/>
       <c r="AF22" s="128"/>
@@ -4553,11 +4538,11 @@
       <c r="AK22" s="127"/>
       <c r="AL22" s="127"/>
       <c r="AM22" s="129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO22" s="85"/>
       <c r="AP22" s="107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AQ22" s="107"/>
       <c r="AR22" s="107"/>
@@ -4568,7 +4553,7 @@
       <c r="AW22" s="107"/>
       <c r="AX22" s="107"/>
       <c r="AY22" s="99" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AZ22" s="99"/>
       <c r="BA22" s="99"/>
@@ -4602,7 +4587,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="131" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23" s="131"/>
       <c r="D23" s="131"/>
@@ -4611,17 +4596,17 @@
       <c r="G23" s="131"/>
       <c r="H23" s="123"/>
       <c r="I23" s="124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J23" s="124"/>
       <c r="K23" s="124"/>
       <c r="L23" s="125"/>
       <c r="M23" s="124"/>
       <c r="N23" s="124" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O23" s="126" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P23" s="127"/>
       <c r="Q23" s="127"/>
@@ -4639,7 +4624,7 @@
       <c r="AC23" s="127"/>
       <c r="AD23" s="128"/>
       <c r="AE23" s="132" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF23" s="132"/>
       <c r="AG23" s="132"/>
@@ -4649,11 +4634,11 @@
       <c r="AK23" s="127"/>
       <c r="AL23" s="127"/>
       <c r="AM23" s="129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO23" s="85"/>
       <c r="AP23" s="107" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ23" s="107"/>
       <c r="AR23" s="107"/>
@@ -4664,7 +4649,7 @@
       <c r="AW23" s="107"/>
       <c r="AX23" s="107"/>
       <c r="AY23" s="99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AZ23" s="99"/>
       <c r="BA23" s="99"/>
@@ -4698,7 +4683,7 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="135" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="135"/>
       <c r="D24" s="135"/>
@@ -4707,17 +4692,17 @@
       <c r="G24" s="135"/>
       <c r="H24" s="123"/>
       <c r="I24" s="124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J24" s="124"/>
       <c r="K24" s="124"/>
       <c r="L24" s="136"/>
       <c r="M24" s="124"/>
       <c r="N24" s="124" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O24" s="126" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P24" s="137"/>
       <c r="Q24" s="137"/>
@@ -4735,23 +4720,23 @@
       <c r="AC24" s="124"/>
       <c r="AD24" s="138"/>
       <c r="AE24" s="132" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF24" s="132"/>
       <c r="AG24" s="132"/>
       <c r="AH24" s="124"/>
       <c r="AI24" s="128"/>
       <c r="AJ24" s="128" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK24" s="128"/>
       <c r="AL24" s="128"/>
       <c r="AM24" s="129" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO24" s="85"/>
       <c r="AP24" s="107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AQ24" s="107"/>
       <c r="AR24" s="107"/>
@@ -4762,7 +4747,7 @@
       <c r="AW24" s="107"/>
       <c r="AX24" s="107"/>
       <c r="AY24" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ24" s="99"/>
       <c r="BA24" s="99"/>
@@ -4776,7 +4761,7 @@
       <c r="BG24" s="108"/>
       <c r="BH24" s="108"/>
       <c r="BI24" s="109" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BJ24" s="109"/>
       <c r="BK24" s="109"/>
@@ -4791,22 +4776,22 @@
       <c r="BT24" s="109"/>
       <c r="BU24" s="109"/>
       <c r="BV24" s="139" t="n">
-        <v>2883</v>
+        <v>2583</v>
       </c>
       <c r="BW24" s="139"/>
       <c r="BX24" s="139"/>
       <c r="BY24" s="140" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ24" s="140"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO25" s="85"/>
       <c r="AP25" s="107" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AQ25" s="107"/>
       <c r="AR25" s="107"/>
@@ -4817,7 +4802,7 @@
       <c r="AW25" s="107"/>
       <c r="AX25" s="107"/>
       <c r="AY25" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ25" s="99"/>
       <c r="BA25" s="99"/>
@@ -4831,7 +4816,7 @@
       <c r="BG25" s="108"/>
       <c r="BH25" s="108"/>
       <c r="BI25" s="141" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BJ25" s="141"/>
       <c r="BK25" s="141"/>
@@ -4853,7 +4838,7 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -4861,7 +4846,7 @@
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="142" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I26" s="142"/>
       <c r="J26" s="142"/>
@@ -4896,7 +4881,7 @@
       <c r="AM26" s="142"/>
       <c r="AO26" s="85"/>
       <c r="AP26" s="107" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AQ26" s="107"/>
       <c r="AR26" s="107"/>
@@ -4907,7 +4892,7 @@
       <c r="AW26" s="107"/>
       <c r="AX26" s="107"/>
       <c r="AY26" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ26" s="99"/>
       <c r="BA26" s="99"/>
@@ -4921,7 +4906,7 @@
       <c r="BG26" s="108"/>
       <c r="BH26" s="108"/>
       <c r="BI26" s="109" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BJ26" s="109"/>
       <c r="BK26" s="109"/>
@@ -4941,7 +4926,7 @@
       <c r="BW26" s="110"/>
       <c r="BX26" s="110"/>
       <c r="BY26" s="111" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ26" s="111"/>
     </row>
@@ -4986,7 +4971,7 @@
       <c r="AM27" s="143"/>
       <c r="AO27" s="85"/>
       <c r="AP27" s="107" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AQ27" s="107"/>
       <c r="AR27" s="107"/>
@@ -4997,7 +4982,7 @@
       <c r="AW27" s="107"/>
       <c r="AX27" s="107"/>
       <c r="AY27" s="99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AZ27" s="99"/>
       <c r="BA27" s="99"/>
@@ -5011,7 +4996,7 @@
       <c r="BG27" s="108"/>
       <c r="BH27" s="108"/>
       <c r="BI27" s="121" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BJ27" s="121"/>
       <c r="BK27" s="121"/>
@@ -5033,7 +5018,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="144" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="144"/>
       <c r="D28" s="144"/>
@@ -5041,10 +5026,10 @@
       <c r="F28" s="144"/>
       <c r="G28" s="144"/>
       <c r="H28" s="53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="145" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J28" s="145"/>
       <c r="K28" s="145"/>
@@ -5072,7 +5057,7 @@
       <c r="AG28" s="146"/>
       <c r="AH28" s="146"/>
       <c r="AI28" s="147" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ28" s="148"/>
       <c r="AK28" s="148"/>
@@ -5080,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="AM28" s="150" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AO28" s="85"/>
       <c r="AP28" s="130"/>
@@ -5129,10 +5114,10 @@
       <c r="F29" s="144"/>
       <c r="G29" s="144"/>
       <c r="H29" s="64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="153" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J29" s="153"/>
       <c r="K29" s="153"/>
@@ -5160,7 +5145,7 @@
       <c r="AG29" s="154"/>
       <c r="AH29" s="154"/>
       <c r="AI29" s="155" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ29" s="156"/>
       <c r="AK29" s="156"/>
@@ -5168,7 +5153,7 @@
         <v>40</v>
       </c>
       <c r="AM29" s="158" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AO29" s="85"/>
       <c r="AP29" s="159"/>
@@ -5217,10 +5202,10 @@
       <c r="F30" s="144"/>
       <c r="G30" s="144"/>
       <c r="H30" s="75" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="162" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" s="162"/>
       <c r="K30" s="162"/>
@@ -5248,7 +5233,7 @@
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="163" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ30" s="164"/>
       <c r="AK30" s="164"/>
@@ -5256,13 +5241,13 @@
         <v>28</v>
       </c>
       <c r="AM30" s="166" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AO30" s="167" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AP30" s="168" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ30" s="168"/>
       <c r="AR30" s="168"/>
@@ -5284,7 +5269,7 @@
       <c r="BE30" s="170"/>
       <c r="BF30" s="170"/>
       <c r="BG30" s="111" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BH30" s="111"/>
       <c r="BI30" s="130"/>
@@ -5308,7 +5293,7 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="131" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" s="131"/>
       <c r="D31" s="131"/>
@@ -5322,10 +5307,10 @@
       <c r="L31" s="171"/>
       <c r="M31" s="171"/>
       <c r="N31" s="124" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O31" s="131" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P31" s="131"/>
       <c r="Q31" s="131"/>
@@ -5346,7 +5331,7 @@
       <c r="AD31" s="175"/>
       <c r="AE31" s="175"/>
       <c r="AF31" s="176" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG31" s="177"/>
       <c r="AH31" s="177"/>
@@ -5359,7 +5344,7 @@
       <c r="AM31" s="178"/>
       <c r="AO31" s="167"/>
       <c r="AP31" s="98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ31" s="98"/>
       <c r="AR31" s="98"/>
@@ -5402,7 +5387,7 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="131" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="131"/>
       <c r="D32" s="131"/>
@@ -5416,10 +5401,10 @@
       <c r="L32" s="180"/>
       <c r="M32" s="180"/>
       <c r="N32" s="124" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O32" s="131" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P32" s="131"/>
       <c r="Q32" s="131"/>
@@ -5434,7 +5419,7 @@
       <c r="Z32" s="181"/>
       <c r="AA32" s="181"/>
       <c r="AB32" s="131" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC32" s="131"/>
       <c r="AD32" s="131"/>
@@ -5445,13 +5430,13 @@
       <c r="AI32" s="182"/>
       <c r="AJ32" s="182"/>
       <c r="AK32" s="138" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AL32" s="183"/>
       <c r="AM32" s="183"/>
       <c r="AO32" s="167"/>
       <c r="AP32" s="107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AQ32" s="107"/>
       <c r="AR32" s="107"/>
@@ -5494,7 +5479,7 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="184" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" s="184"/>
       <c r="D33" s="184"/>
@@ -5502,20 +5487,20 @@
       <c r="F33" s="184"/>
       <c r="G33" s="184"/>
       <c r="H33" s="185" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="185"/>
       <c r="J33" s="185"/>
       <c r="K33" s="186"/>
       <c r="L33" s="187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M33" s="188"/>
       <c r="N33" s="94"/>
       <c r="O33" s="189"/>
       <c r="P33" s="187"/>
       <c r="Q33" s="187" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R33" s="189"/>
       <c r="S33" s="189"/>
@@ -5541,7 +5526,7 @@
       <c r="AM33" s="194"/>
       <c r="AO33" s="167"/>
       <c r="AP33" s="107" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AQ33" s="107"/>
       <c r="AR33" s="107"/>
@@ -5593,43 +5578,43 @@
       <c r="I34" s="185"/>
       <c r="J34" s="185"/>
       <c r="K34" s="195" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L34" s="195" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M34" s="195"/>
       <c r="N34" s="195"/>
       <c r="O34" s="195" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="195"/>
       <c r="Q34" s="195" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R34" s="195"/>
       <c r="S34" s="195"/>
       <c r="T34" s="195" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U34" s="195"/>
       <c r="V34" s="195"/>
       <c r="W34" s="195"/>
       <c r="X34" s="195" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Y34" s="195"/>
       <c r="Z34" s="195"/>
       <c r="AA34" s="195" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB34" s="195" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AC34" s="195"/>
       <c r="AD34" s="196"/>
       <c r="AE34" s="196" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AF34" s="197"/>
       <c r="AG34" s="197"/>
@@ -5639,11 +5624,11 @@
       <c r="AK34" s="197"/>
       <c r="AL34" s="197"/>
       <c r="AM34" s="198" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO34" s="167"/>
       <c r="AP34" s="107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ34" s="107"/>
       <c r="AR34" s="107"/>
@@ -5686,7 +5671,7 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="199" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" s="199"/>
       <c r="D35" s="199"/>
@@ -5694,7 +5679,7 @@
       <c r="F35" s="199"/>
       <c r="G35" s="199"/>
       <c r="H35" s="142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="142"/>
       <c r="J35" s="142"/>
@@ -5729,7 +5714,7 @@
       <c r="AM35" s="142"/>
       <c r="AO35" s="167"/>
       <c r="AP35" s="200" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AQ35" s="200"/>
       <c r="AR35" s="200"/>
@@ -5810,7 +5795,7 @@
       <c r="AL36" s="204"/>
       <c r="AM36" s="204"/>
       <c r="AO36" s="42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AP36" s="42"/>
       <c r="AQ36" s="42"/>
@@ -5833,11 +5818,11 @@
       <c r="BE36" s="205"/>
       <c r="BF36" s="205"/>
       <c r="BG36" s="178" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BH36" s="178"/>
       <c r="BI36" s="40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BJ36" s="40"/>
       <c r="BK36" s="40"/>
@@ -5858,7 +5843,7 @@
       <c r="BW36" s="205"/>
       <c r="BX36" s="205"/>
       <c r="BY36" s="178" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BZ36" s="178"/>
     </row>
@@ -5902,12 +5887,12 @@
       <c r="AL37" s="204"/>
       <c r="AM37" s="204"/>
       <c r="AO37" s="24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="144" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C38" s="144"/>
       <c r="D38" s="144"/>
@@ -5915,7 +5900,7 @@
       <c r="F38" s="144"/>
       <c r="G38" s="144"/>
       <c r="H38" s="142" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I38" s="142"/>
       <c r="J38" s="142"/>
@@ -5955,7 +5940,7 @@
       <c r="AR38" s="207"/>
       <c r="AS38" s="207"/>
       <c r="AT38" s="208" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AU38" s="208"/>
       <c r="AV38" s="208"/>
@@ -5963,7 +5948,7 @@
       <c r="AX38" s="208"/>
       <c r="AY38" s="208"/>
       <c r="AZ38" s="209" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BA38" s="209"/>
       <c r="BB38" s="209"/>
@@ -5971,7 +5956,7 @@
       <c r="BD38" s="209"/>
       <c r="BE38" s="209"/>
       <c r="BF38" s="210" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BG38" s="210"/>
       <c r="BH38" s="210"/>
@@ -6125,7 +6110,7 @@
       <c r="AX40" s="208"/>
       <c r="AY40" s="208"/>
       <c r="AZ40" s="212" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BA40" s="213"/>
       <c r="BB40" s="214" t="n">
@@ -6160,7 +6145,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="216" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C41" s="216"/>
       <c r="D41" s="216"/>
@@ -6168,7 +6153,7 @@
       <c r="F41" s="216"/>
       <c r="G41" s="216"/>
       <c r="H41" s="142" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I41" s="142"/>
       <c r="J41" s="142"/>
@@ -6203,7 +6188,7 @@
       <c r="AM41" s="142"/>
       <c r="AN41" s="211"/>
       <c r="AO41" s="217" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AP41" s="217"/>
       <c r="AQ41" s="217"/>
@@ -6216,7 +6201,7 @@
       <c r="AV41" s="218"/>
       <c r="AW41" s="218"/>
       <c r="AX41" s="58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AY41" s="58"/>
       <c r="AZ41" s="219" t="n">
@@ -6226,7 +6211,7 @@
       <c r="BB41" s="219"/>
       <c r="BC41" s="219"/>
       <c r="BD41" s="58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE41" s="58"/>
       <c r="BF41" s="220"/>
@@ -6410,7 +6395,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H44" s="223"/>
       <c r="X44" s="206"/>
@@ -6422,7 +6407,7 @@
       <c r="AD44" s="206"/>
       <c r="AN44" s="224"/>
       <c r="AO44" s="225" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AP44" s="225"/>
       <c r="AQ44" s="225"/>
@@ -6435,17 +6420,17 @@
       <c r="AV44" s="226"/>
       <c r="AW44" s="226"/>
       <c r="AX44" s="69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AY44" s="69"/>
-      <c r="AZ44" s="227" t="n">
+      <c r="AZ44" s="226" t="n">
         <v>94</v>
       </c>
-      <c r="BA44" s="227"/>
-      <c r="BB44" s="227"/>
-      <c r="BC44" s="227"/>
+      <c r="BA44" s="226"/>
+      <c r="BB44" s="226"/>
+      <c r="BC44" s="226"/>
       <c r="BD44" s="69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE44" s="69"/>
       <c r="BF44" s="220"/>
@@ -6472,7 +6457,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="216" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C45" s="216"/>
       <c r="D45" s="216"/>
@@ -6480,17 +6465,17 @@
       <c r="F45" s="216"/>
       <c r="G45" s="216"/>
       <c r="H45" s="216"/>
-      <c r="I45" s="228" t="n">
+      <c r="I45" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="228"/>
-      <c r="K45" s="228"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
       <c r="L45" s="178" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M45" s="178"/>
       <c r="N45" s="216" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O45" s="216"/>
       <c r="P45" s="216"/>
@@ -6500,31 +6485,31 @@
       <c r="T45" s="216"/>
       <c r="U45" s="216"/>
       <c r="V45" s="216"/>
-      <c r="W45" s="229" t="n">
+      <c r="W45" s="228" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="229"/>
-      <c r="Y45" s="229"/>
-      <c r="Z45" s="230" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA45" s="230"/>
-      <c r="AB45" s="231" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC45" s="231"/>
-      <c r="AD45" s="231"/>
-      <c r="AE45" s="231"/>
-      <c r="AF45" s="231"/>
-      <c r="AG45" s="231"/>
-      <c r="AH45" s="232" t="n">
+      <c r="X45" s="228"/>
+      <c r="Y45" s="228"/>
+      <c r="Z45" s="229" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA45" s="229"/>
+      <c r="AB45" s="230" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC45" s="230"/>
+      <c r="AD45" s="230"/>
+      <c r="AE45" s="230"/>
+      <c r="AF45" s="230"/>
+      <c r="AG45" s="230"/>
+      <c r="AH45" s="231" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" s="232"/>
-      <c r="AJ45" s="232"/>
-      <c r="AK45" s="232"/>
+      <c r="AI45" s="231"/>
+      <c r="AJ45" s="231"/>
+      <c r="AK45" s="231"/>
       <c r="AL45" s="89" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AM45" s="89"/>
       <c r="AN45" s="102"/>
@@ -6539,10 +6524,10 @@
       <c r="AW45" s="226"/>
       <c r="AX45" s="69"/>
       <c r="AY45" s="69"/>
-      <c r="AZ45" s="227"/>
-      <c r="BA45" s="227"/>
-      <c r="BB45" s="227"/>
-      <c r="BC45" s="227"/>
+      <c r="AZ45" s="226"/>
+      <c r="BA45" s="226"/>
+      <c r="BB45" s="226"/>
+      <c r="BC45" s="226"/>
       <c r="BD45" s="69"/>
       <c r="BE45" s="69"/>
       <c r="BF45" s="220"/>
@@ -6575,9 +6560,9 @@
       <c r="F46" s="216"/>
       <c r="G46" s="216"/>
       <c r="H46" s="216"/>
-      <c r="I46" s="228"/>
-      <c r="J46" s="228"/>
-      <c r="K46" s="228"/>
+      <c r="I46" s="227"/>
+      <c r="J46" s="227"/>
+      <c r="K46" s="227"/>
       <c r="L46" s="178"/>
       <c r="M46" s="178"/>
       <c r="N46" s="216"/>
@@ -6589,58 +6574,58 @@
       <c r="T46" s="216"/>
       <c r="U46" s="216"/>
       <c r="V46" s="216"/>
-      <c r="W46" s="229"/>
-      <c r="X46" s="229"/>
-      <c r="Y46" s="229"/>
-      <c r="Z46" s="230"/>
-      <c r="AA46" s="230"/>
-      <c r="AB46" s="233" t="s">
-        <v>147</v>
-      </c>
-      <c r="AC46" s="233"/>
-      <c r="AD46" s="233"/>
-      <c r="AE46" s="233"/>
-      <c r="AF46" s="233"/>
-      <c r="AG46" s="233"/>
-      <c r="AH46" s="234" t="n">
+      <c r="W46" s="228"/>
+      <c r="X46" s="228"/>
+      <c r="Y46" s="228"/>
+      <c r="Z46" s="229"/>
+      <c r="AA46" s="229"/>
+      <c r="AB46" s="232" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC46" s="232"/>
+      <c r="AD46" s="232"/>
+      <c r="AE46" s="232"/>
+      <c r="AF46" s="232"/>
+      <c r="AG46" s="232"/>
+      <c r="AH46" s="233" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" s="234"/>
-      <c r="AJ46" s="234"/>
-      <c r="AK46" s="234"/>
-      <c r="AL46" s="235" t="s">
-        <v>144</v>
-      </c>
-      <c r="AM46" s="235"/>
-      <c r="AO46" s="236" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP46" s="237" t="s">
+      <c r="AI46" s="233"/>
+      <c r="AJ46" s="233"/>
+      <c r="AK46" s="233"/>
+      <c r="AL46" s="234" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM46" s="234"/>
+      <c r="AO46" s="235" t="s">
         <v>149</v>
       </c>
-      <c r="AQ46" s="237"/>
-      <c r="AR46" s="237"/>
-      <c r="AS46" s="237"/>
-      <c r="AT46" s="238" t="n">
+      <c r="AP46" s="236" t="s">
+        <v>150</v>
+      </c>
+      <c r="AQ46" s="236"/>
+      <c r="AR46" s="236"/>
+      <c r="AS46" s="236"/>
+      <c r="AT46" s="237" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" s="238"/>
-      <c r="AV46" s="238"/>
-      <c r="AW46" s="238"/>
-      <c r="AX46" s="239" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY46" s="239"/>
-      <c r="AZ46" s="240" t="n">
+      <c r="AU46" s="237"/>
+      <c r="AV46" s="237"/>
+      <c r="AW46" s="237"/>
+      <c r="AX46" s="238" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY46" s="238"/>
+      <c r="AZ46" s="237" t="n">
         <v>0</v>
       </c>
-      <c r="BA46" s="240"/>
-      <c r="BB46" s="240"/>
-      <c r="BC46" s="240"/>
-      <c r="BD46" s="241" t="s">
-        <v>37</v>
-      </c>
-      <c r="BE46" s="241"/>
+      <c r="BA46" s="237"/>
+      <c r="BB46" s="237"/>
+      <c r="BC46" s="237"/>
+      <c r="BD46" s="239" t="s">
+        <v>38</v>
+      </c>
+      <c r="BE46" s="239"/>
       <c r="BF46" s="220"/>
       <c r="BG46" s="220"/>
       <c r="BH46" s="220"/>
@@ -6665,28 +6650,28 @@
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="102" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C47" s="102" t="s">
-        <v>151</v>
-      </c>
-      <c r="AO47" s="236"/>
-      <c r="AP47" s="237"/>
-      <c r="AQ47" s="237"/>
-      <c r="AR47" s="237"/>
-      <c r="AS47" s="237"/>
-      <c r="AT47" s="238"/>
-      <c r="AU47" s="238"/>
-      <c r="AV47" s="238"/>
-      <c r="AW47" s="238"/>
-      <c r="AX47" s="239"/>
-      <c r="AY47" s="239"/>
-      <c r="AZ47" s="240"/>
-      <c r="BA47" s="240"/>
-      <c r="BB47" s="240"/>
-      <c r="BC47" s="240"/>
-      <c r="BD47" s="241"/>
-      <c r="BE47" s="241"/>
+        <v>152</v>
+      </c>
+      <c r="AO47" s="235"/>
+      <c r="AP47" s="236"/>
+      <c r="AQ47" s="236"/>
+      <c r="AR47" s="236"/>
+      <c r="AS47" s="236"/>
+      <c r="AT47" s="237"/>
+      <c r="AU47" s="237"/>
+      <c r="AV47" s="237"/>
+      <c r="AW47" s="237"/>
+      <c r="AX47" s="238"/>
+      <c r="AY47" s="238"/>
+      <c r="AZ47" s="237"/>
+      <c r="BA47" s="237"/>
+      <c r="BB47" s="237"/>
+      <c r="BC47" s="237"/>
+      <c r="BD47" s="239"/>
+      <c r="BE47" s="239"/>
       <c r="BF47" s="220"/>
       <c r="BG47" s="220"/>
       <c r="BH47" s="220"/>
@@ -6711,33 +6696,33 @@
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="AO48" s="236"/>
-      <c r="AP48" s="242" t="s">
         <v>153</v>
       </c>
-      <c r="AQ48" s="242"/>
-      <c r="AR48" s="242"/>
-      <c r="AS48" s="242"/>
+      <c r="AO48" s="235"/>
+      <c r="AP48" s="240" t="s">
+        <v>154</v>
+      </c>
+      <c r="AQ48" s="240"/>
+      <c r="AR48" s="240"/>
+      <c r="AS48" s="240"/>
       <c r="AT48" s="226" t="n">
         <v>12</v>
       </c>
       <c r="AU48" s="226"/>
       <c r="AV48" s="226"/>
       <c r="AW48" s="226"/>
-      <c r="AX48" s="243" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY48" s="243"/>
-      <c r="AZ48" s="227" t="n">
+      <c r="AX48" s="241" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY48" s="241"/>
+      <c r="AZ48" s="226" t="n">
         <v>12</v>
       </c>
-      <c r="BA48" s="227"/>
-      <c r="BB48" s="227"/>
-      <c r="BC48" s="227"/>
+      <c r="BA48" s="226"/>
+      <c r="BB48" s="226"/>
+      <c r="BC48" s="226"/>
       <c r="BD48" s="69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE48" s="69"/>
       <c r="BF48" s="220"/>
@@ -6763,46 +6748,46 @@
       <c r="BZ48" s="220"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="244"/>
-      <c r="C49" s="245" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="245"/>
-      <c r="E49" s="245"/>
-      <c r="F49" s="245"/>
-      <c r="G49" s="245"/>
-      <c r="H49" s="245"/>
-      <c r="I49" s="245"/>
-      <c r="J49" s="245"/>
-      <c r="K49" s="245"/>
-      <c r="L49" s="245"/>
-      <c r="M49" s="245"/>
-      <c r="N49" s="245"/>
-      <c r="O49" s="246" t="s">
+      <c r="B49" s="242"/>
+      <c r="C49" s="243" t="s">
         <v>155</v>
       </c>
-      <c r="P49" s="246"/>
-      <c r="Q49" s="246"/>
-      <c r="R49" s="246"/>
-      <c r="S49" s="246"/>
-      <c r="T49" s="246"/>
-      <c r="U49" s="247" t="s">
+      <c r="D49" s="243"/>
+      <c r="E49" s="243"/>
+      <c r="F49" s="243"/>
+      <c r="G49" s="243"/>
+      <c r="H49" s="243"/>
+      <c r="I49" s="243"/>
+      <c r="J49" s="243"/>
+      <c r="K49" s="243"/>
+      <c r="L49" s="243"/>
+      <c r="M49" s="243"/>
+      <c r="N49" s="243"/>
+      <c r="O49" s="244" t="s">
         <v>156</v>
       </c>
-      <c r="V49" s="247"/>
-      <c r="W49" s="247"/>
-      <c r="X49" s="248" t="s">
+      <c r="P49" s="244"/>
+      <c r="Q49" s="244"/>
+      <c r="R49" s="244"/>
+      <c r="S49" s="244"/>
+      <c r="T49" s="244"/>
+      <c r="U49" s="245" t="s">
         <v>157</v>
       </c>
-      <c r="Y49" s="248"/>
-      <c r="Z49" s="248"/>
-      <c r="AA49" s="249" t="s">
+      <c r="V49" s="245"/>
+      <c r="W49" s="245"/>
+      <c r="X49" s="246" t="s">
         <v>158</v>
       </c>
-      <c r="AB49" s="249"/>
-      <c r="AC49" s="249"/>
+      <c r="Y49" s="246"/>
+      <c r="Z49" s="246"/>
+      <c r="AA49" s="247" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB49" s="247"/>
+      <c r="AC49" s="247"/>
       <c r="AD49" s="47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AE49" s="47"/>
       <c r="AF49" s="47"/>
@@ -6813,21 +6798,21 @@
       <c r="AK49" s="47"/>
       <c r="AL49" s="47"/>
       <c r="AM49" s="47"/>
-      <c r="AO49" s="236"/>
-      <c r="AP49" s="242"/>
-      <c r="AQ49" s="242"/>
-      <c r="AR49" s="242"/>
-      <c r="AS49" s="242"/>
+      <c r="AO49" s="235"/>
+      <c r="AP49" s="240"/>
+      <c r="AQ49" s="240"/>
+      <c r="AR49" s="240"/>
+      <c r="AS49" s="240"/>
       <c r="AT49" s="226"/>
       <c r="AU49" s="226"/>
       <c r="AV49" s="226"/>
       <c r="AW49" s="226"/>
-      <c r="AX49" s="243"/>
-      <c r="AY49" s="243"/>
-      <c r="AZ49" s="227"/>
-      <c r="BA49" s="227"/>
-      <c r="BB49" s="227"/>
-      <c r="BC49" s="227"/>
+      <c r="AX49" s="241"/>
+      <c r="AY49" s="241"/>
+      <c r="AZ49" s="226"/>
+      <c r="BA49" s="226"/>
+      <c r="BB49" s="226"/>
+      <c r="BC49" s="226"/>
       <c r="BD49" s="69"/>
       <c r="BE49" s="69"/>
       <c r="BF49" s="220"/>
@@ -6853,38 +6838,38 @@
       <c r="BZ49" s="220"/>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="244"/>
-      <c r="C50" s="250" t="s">
-        <v>160</v>
-      </c>
-      <c r="D50" s="250"/>
-      <c r="E50" s="250"/>
-      <c r="F50" s="250"/>
-      <c r="G50" s="250"/>
-      <c r="H50" s="250"/>
-      <c r="I50" s="250"/>
-      <c r="J50" s="250"/>
-      <c r="K50" s="250"/>
-      <c r="L50" s="250"/>
-      <c r="M50" s="250"/>
-      <c r="N50" s="250"/>
-      <c r="O50" s="246"/>
-      <c r="P50" s="246"/>
-      <c r="Q50" s="246"/>
-      <c r="R50" s="246"/>
-      <c r="S50" s="246"/>
-      <c r="T50" s="246"/>
-      <c r="U50" s="247"/>
-      <c r="V50" s="247"/>
-      <c r="W50" s="247"/>
-      <c r="X50" s="248"/>
-      <c r="Y50" s="248"/>
-      <c r="Z50" s="248"/>
-      <c r="AA50" s="251" t="s">
+      <c r="B50" s="242"/>
+      <c r="C50" s="248" t="s">
         <v>161</v>
       </c>
-      <c r="AB50" s="251"/>
-      <c r="AC50" s="251"/>
+      <c r="D50" s="248"/>
+      <c r="E50" s="248"/>
+      <c r="F50" s="248"/>
+      <c r="G50" s="248"/>
+      <c r="H50" s="248"/>
+      <c r="I50" s="248"/>
+      <c r="J50" s="248"/>
+      <c r="K50" s="248"/>
+      <c r="L50" s="248"/>
+      <c r="M50" s="248"/>
+      <c r="N50" s="248"/>
+      <c r="O50" s="244"/>
+      <c r="P50" s="244"/>
+      <c r="Q50" s="244"/>
+      <c r="R50" s="244"/>
+      <c r="S50" s="244"/>
+      <c r="T50" s="244"/>
+      <c r="U50" s="245"/>
+      <c r="V50" s="245"/>
+      <c r="W50" s="245"/>
+      <c r="X50" s="246"/>
+      <c r="Y50" s="246"/>
+      <c r="Z50" s="246"/>
+      <c r="AA50" s="249" t="s">
+        <v>162</v>
+      </c>
+      <c r="AB50" s="249"/>
+      <c r="AC50" s="249"/>
       <c r="AD50" s="47"/>
       <c r="AE50" s="47"/>
       <c r="AF50" s="47"/>
@@ -6895,33 +6880,33 @@
       <c r="AK50" s="47"/>
       <c r="AL50" s="47"/>
       <c r="AM50" s="47"/>
-      <c r="AO50" s="236"/>
-      <c r="AP50" s="252" t="s">
-        <v>162</v>
-      </c>
-      <c r="AQ50" s="252"/>
-      <c r="AR50" s="252"/>
-      <c r="AS50" s="252"/>
-      <c r="AT50" s="238" t="n">
+      <c r="AO50" s="235"/>
+      <c r="AP50" s="250" t="s">
+        <v>163</v>
+      </c>
+      <c r="AQ50" s="250"/>
+      <c r="AR50" s="250"/>
+      <c r="AS50" s="250"/>
+      <c r="AT50" s="237" t="n">
         <v>4</v>
       </c>
-      <c r="AU50" s="238"/>
-      <c r="AV50" s="238"/>
-      <c r="AW50" s="238"/>
-      <c r="AX50" s="239" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY50" s="239"/>
-      <c r="AZ50" s="240" t="n">
+      <c r="AU50" s="237"/>
+      <c r="AV50" s="237"/>
+      <c r="AW50" s="237"/>
+      <c r="AX50" s="238" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY50" s="238"/>
+      <c r="AZ50" s="237" t="n">
         <v>4</v>
       </c>
-      <c r="BA50" s="240"/>
-      <c r="BB50" s="240"/>
-      <c r="BC50" s="240"/>
-      <c r="BD50" s="241" t="s">
-        <v>37</v>
-      </c>
-      <c r="BE50" s="241"/>
+      <c r="BA50" s="237"/>
+      <c r="BB50" s="237"/>
+      <c r="BC50" s="237"/>
+      <c r="BD50" s="239" t="s">
+        <v>38</v>
+      </c>
+      <c r="BE50" s="239"/>
       <c r="BF50" s="220"/>
       <c r="BG50" s="220"/>
       <c r="BH50" s="220"/>
@@ -6945,77 +6930,77 @@
       <c r="BZ50" s="220"/>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="253" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" s="254" t="s">
+      <c r="B51" s="251" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="254"/>
-      <c r="E51" s="254"/>
-      <c r="F51" s="254"/>
-      <c r="G51" s="254"/>
-      <c r="H51" s="254"/>
-      <c r="I51" s="254"/>
-      <c r="J51" s="254"/>
-      <c r="K51" s="254"/>
-      <c r="L51" s="254"/>
-      <c r="M51" s="254"/>
-      <c r="N51" s="254"/>
-      <c r="O51" s="255" t="s">
+      <c r="C51" s="252" t="s">
         <v>165</v>
       </c>
-      <c r="P51" s="255"/>
-      <c r="Q51" s="255"/>
-      <c r="R51" s="255"/>
-      <c r="S51" s="255"/>
-      <c r="T51" s="255"/>
-      <c r="U51" s="256"/>
-      <c r="V51" s="256"/>
-      <c r="W51" s="257" t="n">
+      <c r="D51" s="252"/>
+      <c r="E51" s="252"/>
+      <c r="F51" s="252"/>
+      <c r="G51" s="252"/>
+      <c r="H51" s="252"/>
+      <c r="I51" s="252"/>
+      <c r="J51" s="252"/>
+      <c r="K51" s="252"/>
+      <c r="L51" s="252"/>
+      <c r="M51" s="252"/>
+      <c r="N51" s="252"/>
+      <c r="O51" s="253" t="s">
+        <v>166</v>
+      </c>
+      <c r="P51" s="253"/>
+      <c r="Q51" s="253"/>
+      <c r="R51" s="253"/>
+      <c r="S51" s="253"/>
+      <c r="T51" s="253"/>
+      <c r="U51" s="254"/>
+      <c r="V51" s="254"/>
+      <c r="W51" s="255" t="n">
         <v>70</v>
       </c>
-      <c r="X51" s="258"/>
-      <c r="Y51" s="258"/>
-      <c r="Z51" s="257" t="n">
+      <c r="X51" s="256"/>
+      <c r="Y51" s="256"/>
+      <c r="Z51" s="255" t="n">
         <v>80</v>
       </c>
-      <c r="AA51" s="259"/>
-      <c r="AB51" s="259"/>
-      <c r="AC51" s="260" t="n">
+      <c r="AA51" s="257"/>
+      <c r="AB51" s="257"/>
+      <c r="AC51" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="AD51" s="261"/>
-      <c r="AE51" s="261"/>
-      <c r="AF51" s="261"/>
-      <c r="AG51" s="262" t="n">
+      <c r="AD51" s="259"/>
+      <c r="AE51" s="259"/>
+      <c r="AF51" s="259"/>
+      <c r="AG51" s="260" t="n">
         <v>30</v>
       </c>
-      <c r="AH51" s="262"/>
+      <c r="AH51" s="260"/>
       <c r="AI51" s="148"/>
       <c r="AJ51" s="148"/>
       <c r="AK51" s="148"/>
-      <c r="AL51" s="263" t="n">
+      <c r="AL51" s="261" t="n">
         <v>60</v>
       </c>
-      <c r="AM51" s="263"/>
-      <c r="AO51" s="236"/>
-      <c r="AP51" s="252"/>
-      <c r="AQ51" s="252"/>
-      <c r="AR51" s="252"/>
-      <c r="AS51" s="252"/>
-      <c r="AT51" s="238"/>
-      <c r="AU51" s="238"/>
-      <c r="AV51" s="238"/>
-      <c r="AW51" s="238"/>
-      <c r="AX51" s="239"/>
-      <c r="AY51" s="239"/>
-      <c r="AZ51" s="240"/>
-      <c r="BA51" s="240"/>
-      <c r="BB51" s="240"/>
-      <c r="BC51" s="240"/>
-      <c r="BD51" s="241"/>
-      <c r="BE51" s="241"/>
+      <c r="AM51" s="261"/>
+      <c r="AO51" s="235"/>
+      <c r="AP51" s="250"/>
+      <c r="AQ51" s="250"/>
+      <c r="AR51" s="250"/>
+      <c r="AS51" s="250"/>
+      <c r="AT51" s="237"/>
+      <c r="AU51" s="237"/>
+      <c r="AV51" s="237"/>
+      <c r="AW51" s="237"/>
+      <c r="AX51" s="238"/>
+      <c r="AY51" s="238"/>
+      <c r="AZ51" s="237"/>
+      <c r="BA51" s="237"/>
+      <c r="BB51" s="237"/>
+      <c r="BC51" s="237"/>
+      <c r="BD51" s="239"/>
+      <c r="BE51" s="239"/>
       <c r="BF51" s="220"/>
       <c r="BG51" s="220"/>
       <c r="BH51" s="220"/>
@@ -7039,71 +7024,71 @@
       <c r="BZ51" s="220"/>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="253"/>
-      <c r="C52" s="264"/>
-      <c r="D52" s="264"/>
-      <c r="E52" s="264"/>
-      <c r="F52" s="264"/>
-      <c r="G52" s="264"/>
-      <c r="H52" s="264"/>
-      <c r="I52" s="264"/>
-      <c r="J52" s="264"/>
-      <c r="K52" s="264"/>
-      <c r="L52" s="264"/>
-      <c r="M52" s="264"/>
-      <c r="N52" s="264"/>
-      <c r="O52" s="255"/>
-      <c r="P52" s="255"/>
-      <c r="Q52" s="255"/>
-      <c r="R52" s="255"/>
-      <c r="S52" s="255"/>
-      <c r="T52" s="255"/>
-      <c r="U52" s="256"/>
-      <c r="V52" s="256"/>
-      <c r="W52" s="257"/>
-      <c r="X52" s="258"/>
-      <c r="Y52" s="258"/>
-      <c r="Z52" s="257"/>
-      <c r="AA52" s="265"/>
-      <c r="AB52" s="265"/>
-      <c r="AC52" s="241" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD52" s="261"/>
-      <c r="AE52" s="261"/>
-      <c r="AF52" s="261"/>
-      <c r="AG52" s="262"/>
-      <c r="AH52" s="262"/>
+      <c r="B52" s="251"/>
+      <c r="C52" s="262"/>
+      <c r="D52" s="262"/>
+      <c r="E52" s="262"/>
+      <c r="F52" s="262"/>
+      <c r="G52" s="262"/>
+      <c r="H52" s="262"/>
+      <c r="I52" s="262"/>
+      <c r="J52" s="262"/>
+      <c r="K52" s="262"/>
+      <c r="L52" s="262"/>
+      <c r="M52" s="262"/>
+      <c r="N52" s="262"/>
+      <c r="O52" s="253"/>
+      <c r="P52" s="253"/>
+      <c r="Q52" s="253"/>
+      <c r="R52" s="253"/>
+      <c r="S52" s="253"/>
+      <c r="T52" s="253"/>
+      <c r="U52" s="254"/>
+      <c r="V52" s="254"/>
+      <c r="W52" s="255"/>
+      <c r="X52" s="256"/>
+      <c r="Y52" s="256"/>
+      <c r="Z52" s="255"/>
+      <c r="AA52" s="263"/>
+      <c r="AB52" s="263"/>
+      <c r="AC52" s="239" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD52" s="259"/>
+      <c r="AE52" s="259"/>
+      <c r="AF52" s="259"/>
+      <c r="AG52" s="260"/>
+      <c r="AH52" s="260"/>
       <c r="AI52" s="148"/>
       <c r="AJ52" s="148"/>
       <c r="AK52" s="148"/>
-      <c r="AL52" s="263"/>
-      <c r="AM52" s="263"/>
-      <c r="AO52" s="236"/>
-      <c r="AP52" s="242" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ52" s="242"/>
-      <c r="AR52" s="242"/>
-      <c r="AS52" s="242"/>
+      <c r="AL52" s="261"/>
+      <c r="AM52" s="261"/>
+      <c r="AO52" s="235"/>
+      <c r="AP52" s="240" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ52" s="240"/>
+      <c r="AR52" s="240"/>
+      <c r="AS52" s="240"/>
       <c r="AT52" s="226" t="n">
         <v>37</v>
       </c>
       <c r="AU52" s="226"/>
       <c r="AV52" s="226"/>
       <c r="AW52" s="226"/>
-      <c r="AX52" s="243" t="s">
+      <c r="AX52" s="241" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY52" s="241"/>
+      <c r="AZ52" s="226" t="n">
         <v>37</v>
       </c>
-      <c r="AY52" s="243"/>
-      <c r="AZ52" s="227" t="n">
-        <v>37</v>
-      </c>
-      <c r="BA52" s="227"/>
-      <c r="BB52" s="227"/>
-      <c r="BC52" s="227"/>
+      <c r="BA52" s="226"/>
+      <c r="BB52" s="226"/>
+      <c r="BC52" s="226"/>
       <c r="BD52" s="69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE52" s="69"/>
       <c r="BF52" s="220"/>
@@ -7129,73 +7114,73 @@
       <c r="BZ52" s="220"/>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="253"/>
-      <c r="C53" s="266" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="266"/>
-      <c r="E53" s="266"/>
-      <c r="F53" s="266"/>
-      <c r="G53" s="266"/>
-      <c r="H53" s="266"/>
-      <c r="I53" s="266"/>
-      <c r="J53" s="266"/>
-      <c r="K53" s="266"/>
-      <c r="L53" s="266"/>
-      <c r="M53" s="266"/>
-      <c r="N53" s="266"/>
-      <c r="O53" s="267" t="s">
+      <c r="B53" s="251"/>
+      <c r="C53" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="P53" s="267"/>
-      <c r="Q53" s="267"/>
-      <c r="R53" s="267"/>
-      <c r="S53" s="267"/>
-      <c r="T53" s="267"/>
-      <c r="U53" s="268"/>
-      <c r="V53" s="268"/>
-      <c r="W53" s="269" t="n">
+      <c r="D53" s="264"/>
+      <c r="E53" s="264"/>
+      <c r="F53" s="264"/>
+      <c r="G53" s="264"/>
+      <c r="H53" s="264"/>
+      <c r="I53" s="264"/>
+      <c r="J53" s="264"/>
+      <c r="K53" s="264"/>
+      <c r="L53" s="264"/>
+      <c r="M53" s="264"/>
+      <c r="N53" s="264"/>
+      <c r="O53" s="265" t="s">
+        <v>168</v>
+      </c>
+      <c r="P53" s="265"/>
+      <c r="Q53" s="265"/>
+      <c r="R53" s="265"/>
+      <c r="S53" s="265"/>
+      <c r="T53" s="265"/>
+      <c r="U53" s="266"/>
+      <c r="V53" s="266"/>
+      <c r="W53" s="267" t="n">
         <v>30</v>
       </c>
-      <c r="X53" s="270"/>
-      <c r="Y53" s="270"/>
-      <c r="Z53" s="269" t="n">
+      <c r="X53" s="268"/>
+      <c r="Y53" s="268"/>
+      <c r="Z53" s="267" t="n">
         <v>100</v>
       </c>
-      <c r="AA53" s="271"/>
-      <c r="AB53" s="271"/>
-      <c r="AC53" s="272" t="n">
+      <c r="AA53" s="269"/>
+      <c r="AB53" s="269"/>
+      <c r="AC53" s="270" t="n">
         <v>0</v>
       </c>
-      <c r="AD53" s="273"/>
-      <c r="AE53" s="273"/>
-      <c r="AF53" s="273"/>
-      <c r="AG53" s="274" t="n">
+      <c r="AD53" s="271"/>
+      <c r="AE53" s="271"/>
+      <c r="AF53" s="271"/>
+      <c r="AG53" s="272" t="n">
         <v>31</v>
       </c>
-      <c r="AH53" s="274"/>
+      <c r="AH53" s="272"/>
       <c r="AI53" s="156"/>
       <c r="AJ53" s="156"/>
       <c r="AK53" s="156"/>
-      <c r="AL53" s="275" t="n">
+      <c r="AL53" s="273" t="n">
         <v>90</v>
       </c>
-      <c r="AM53" s="275"/>
-      <c r="AO53" s="236"/>
-      <c r="AP53" s="242"/>
-      <c r="AQ53" s="242"/>
-      <c r="AR53" s="242"/>
-      <c r="AS53" s="242"/>
+      <c r="AM53" s="273"/>
+      <c r="AO53" s="235"/>
+      <c r="AP53" s="240"/>
+      <c r="AQ53" s="240"/>
+      <c r="AR53" s="240"/>
+      <c r="AS53" s="240"/>
       <c r="AT53" s="226"/>
       <c r="AU53" s="226"/>
       <c r="AV53" s="226"/>
       <c r="AW53" s="226"/>
-      <c r="AX53" s="243"/>
-      <c r="AY53" s="243"/>
-      <c r="AZ53" s="227"/>
-      <c r="BA53" s="227"/>
-      <c r="BB53" s="227"/>
-      <c r="BC53" s="227"/>
+      <c r="AX53" s="241"/>
+      <c r="AY53" s="241"/>
+      <c r="AZ53" s="226"/>
+      <c r="BA53" s="226"/>
+      <c r="BB53" s="226"/>
+      <c r="BC53" s="226"/>
       <c r="BD53" s="69"/>
       <c r="BE53" s="69"/>
       <c r="BF53" s="220"/>
@@ -7221,73 +7206,73 @@
       <c r="BZ53" s="220"/>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="253"/>
-      <c r="C54" s="264"/>
-      <c r="D54" s="264"/>
-      <c r="E54" s="264"/>
-      <c r="F54" s="264"/>
-      <c r="G54" s="264"/>
-      <c r="H54" s="264"/>
-      <c r="I54" s="264"/>
-      <c r="J54" s="264"/>
-      <c r="K54" s="264"/>
-      <c r="L54" s="264"/>
-      <c r="M54" s="264"/>
-      <c r="N54" s="264"/>
-      <c r="O54" s="267"/>
-      <c r="P54" s="267"/>
-      <c r="Q54" s="267"/>
-      <c r="R54" s="267"/>
-      <c r="S54" s="267"/>
-      <c r="T54" s="267"/>
-      <c r="U54" s="268"/>
-      <c r="V54" s="268"/>
-      <c r="W54" s="269"/>
-      <c r="X54" s="270"/>
-      <c r="Y54" s="270"/>
-      <c r="Z54" s="269"/>
-      <c r="AA54" s="276"/>
-      <c r="AB54" s="276"/>
-      <c r="AC54" s="277" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD54" s="273"/>
-      <c r="AE54" s="273"/>
-      <c r="AF54" s="273"/>
-      <c r="AG54" s="274"/>
-      <c r="AH54" s="274"/>
+      <c r="B54" s="251"/>
+      <c r="C54" s="262"/>
+      <c r="D54" s="262"/>
+      <c r="E54" s="262"/>
+      <c r="F54" s="262"/>
+      <c r="G54" s="262"/>
+      <c r="H54" s="262"/>
+      <c r="I54" s="262"/>
+      <c r="J54" s="262"/>
+      <c r="K54" s="262"/>
+      <c r="L54" s="262"/>
+      <c r="M54" s="262"/>
+      <c r="N54" s="262"/>
+      <c r="O54" s="265"/>
+      <c r="P54" s="265"/>
+      <c r="Q54" s="265"/>
+      <c r="R54" s="265"/>
+      <c r="S54" s="265"/>
+      <c r="T54" s="265"/>
+      <c r="U54" s="266"/>
+      <c r="V54" s="266"/>
+      <c r="W54" s="267"/>
+      <c r="X54" s="268"/>
+      <c r="Y54" s="268"/>
+      <c r="Z54" s="267"/>
+      <c r="AA54" s="274"/>
+      <c r="AB54" s="274"/>
+      <c r="AC54" s="275" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD54" s="271"/>
+      <c r="AE54" s="271"/>
+      <c r="AF54" s="271"/>
+      <c r="AG54" s="272"/>
+      <c r="AH54" s="272"/>
       <c r="AI54" s="156"/>
       <c r="AJ54" s="156"/>
       <c r="AK54" s="156"/>
-      <c r="AL54" s="275"/>
-      <c r="AM54" s="275"/>
-      <c r="AO54" s="236"/>
-      <c r="AP54" s="278" t="s">
-        <v>168</v>
-      </c>
-      <c r="AQ54" s="278"/>
-      <c r="AR54" s="278"/>
-      <c r="AS54" s="278"/>
-      <c r="AT54" s="279" t="n">
+      <c r="AL54" s="273"/>
+      <c r="AM54" s="273"/>
+      <c r="AO54" s="235"/>
+      <c r="AP54" s="276" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ54" s="276"/>
+      <c r="AR54" s="276"/>
+      <c r="AS54" s="276"/>
+      <c r="AT54" s="277" t="n">
         <f aca="false">IF(AND(AT46="",AT48="",AT50="",AT52=""),"",SUM(AT46:AW53))</f>
         <v>53</v>
       </c>
-      <c r="AU54" s="279"/>
-      <c r="AV54" s="279"/>
-      <c r="AW54" s="279"/>
-      <c r="AX54" s="280" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY54" s="280"/>
-      <c r="AZ54" s="281" t="n">
+      <c r="AU54" s="277"/>
+      <c r="AV54" s="277"/>
+      <c r="AW54" s="277"/>
+      <c r="AX54" s="278" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY54" s="278"/>
+      <c r="AZ54" s="277" t="n">
         <f aca="false">IF(AND(AZ46="",AZ48="",AZ50="",AZ52=""),"",SUM(AZ46:AZ53))</f>
         <v>53</v>
       </c>
-      <c r="BA54" s="281"/>
-      <c r="BB54" s="281"/>
-      <c r="BC54" s="281"/>
+      <c r="BA54" s="277"/>
+      <c r="BB54" s="277"/>
+      <c r="BC54" s="277"/>
       <c r="BD54" s="80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE54" s="80"/>
       <c r="BF54" s="220"/>
@@ -7313,73 +7298,73 @@
       <c r="BZ54" s="220"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="253"/>
-      <c r="C55" s="282"/>
-      <c r="D55" s="282"/>
-      <c r="E55" s="282"/>
-      <c r="F55" s="282"/>
-      <c r="G55" s="282"/>
-      <c r="H55" s="282"/>
-      <c r="I55" s="282"/>
-      <c r="J55" s="282"/>
-      <c r="K55" s="282"/>
-      <c r="L55" s="282"/>
-      <c r="M55" s="282"/>
-      <c r="N55" s="282"/>
-      <c r="O55" s="283" t="s">
-        <v>169</v>
-      </c>
-      <c r="P55" s="283"/>
+      <c r="B55" s="251"/>
+      <c r="C55" s="279"/>
+      <c r="D55" s="279"/>
+      <c r="E55" s="279"/>
+      <c r="F55" s="279"/>
+      <c r="G55" s="279"/>
+      <c r="H55" s="279"/>
+      <c r="I55" s="279"/>
+      <c r="J55" s="279"/>
+      <c r="K55" s="279"/>
+      <c r="L55" s="279"/>
+      <c r="M55" s="279"/>
+      <c r="N55" s="279"/>
+      <c r="O55" s="280" t="s">
+        <v>170</v>
+      </c>
+      <c r="P55" s="280"/>
       <c r="Q55" s="117"/>
       <c r="R55" s="117"/>
       <c r="S55" s="117"/>
-      <c r="T55" s="284" t="n">
+      <c r="T55" s="281" t="n">
         <v>1</v>
       </c>
-      <c r="U55" s="285"/>
-      <c r="V55" s="285"/>
+      <c r="U55" s="282"/>
+      <c r="V55" s="282"/>
       <c r="W55" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="X55" s="270"/>
-      <c r="Y55" s="270"/>
+        <v>171</v>
+      </c>
+      <c r="X55" s="268"/>
+      <c r="Y55" s="268"/>
       <c r="Z55" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA55" s="271"/>
-      <c r="AB55" s="271"/>
-      <c r="AC55" s="286" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD55" s="273"/>
-      <c r="AE55" s="273"/>
-      <c r="AF55" s="273"/>
-      <c r="AG55" s="243" t="s">
         <v>171</v>
       </c>
-      <c r="AH55" s="243"/>
+      <c r="AA55" s="269"/>
+      <c r="AB55" s="269"/>
+      <c r="AC55" s="283" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD55" s="271"/>
+      <c r="AE55" s="271"/>
+      <c r="AF55" s="271"/>
+      <c r="AG55" s="241" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH55" s="241"/>
       <c r="AI55" s="156"/>
       <c r="AJ55" s="156"/>
       <c r="AK55" s="156"/>
-      <c r="AL55" s="287" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM55" s="287"/>
-      <c r="AO55" s="236"/>
-      <c r="AP55" s="278"/>
-      <c r="AQ55" s="278"/>
-      <c r="AR55" s="278"/>
-      <c r="AS55" s="278"/>
-      <c r="AT55" s="279"/>
-      <c r="AU55" s="279"/>
-      <c r="AV55" s="279"/>
-      <c r="AW55" s="279"/>
-      <c r="AX55" s="280"/>
-      <c r="AY55" s="280"/>
-      <c r="AZ55" s="281"/>
-      <c r="BA55" s="281"/>
-      <c r="BB55" s="281"/>
-      <c r="BC55" s="281"/>
+      <c r="AL55" s="284" t="s">
+        <v>173</v>
+      </c>
+      <c r="AM55" s="284"/>
+      <c r="AO55" s="235"/>
+      <c r="AP55" s="276"/>
+      <c r="AQ55" s="276"/>
+      <c r="AR55" s="276"/>
+      <c r="AS55" s="276"/>
+      <c r="AT55" s="277"/>
+      <c r="AU55" s="277"/>
+      <c r="AV55" s="277"/>
+      <c r="AW55" s="277"/>
+      <c r="AX55" s="278"/>
+      <c r="AY55" s="278"/>
+      <c r="AZ55" s="277"/>
+      <c r="BA55" s="277"/>
+      <c r="BB55" s="277"/>
+      <c r="BC55" s="277"/>
       <c r="BD55" s="80"/>
       <c r="BE55" s="80"/>
       <c r="BF55" s="220"/>
@@ -7405,77 +7390,77 @@
       <c r="BZ55" s="220"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="253"/>
-      <c r="C56" s="282"/>
-      <c r="D56" s="282"/>
-      <c r="E56" s="282"/>
-      <c r="F56" s="282"/>
-      <c r="G56" s="282"/>
-      <c r="H56" s="282"/>
-      <c r="I56" s="282"/>
-      <c r="J56" s="282"/>
-      <c r="K56" s="282"/>
-      <c r="L56" s="282"/>
-      <c r="M56" s="282"/>
-      <c r="N56" s="282"/>
-      <c r="O56" s="283"/>
-      <c r="P56" s="283"/>
+      <c r="B56" s="251"/>
+      <c r="C56" s="279"/>
+      <c r="D56" s="279"/>
+      <c r="E56" s="279"/>
+      <c r="F56" s="279"/>
+      <c r="G56" s="279"/>
+      <c r="H56" s="279"/>
+      <c r="I56" s="279"/>
+      <c r="J56" s="279"/>
+      <c r="K56" s="279"/>
+      <c r="L56" s="279"/>
+      <c r="M56" s="279"/>
+      <c r="N56" s="279"/>
+      <c r="O56" s="280"/>
+      <c r="P56" s="280"/>
       <c r="Q56" s="117"/>
       <c r="R56" s="117"/>
       <c r="S56" s="117"/>
-      <c r="T56" s="284"/>
-      <c r="U56" s="285"/>
-      <c r="V56" s="285"/>
+      <c r="T56" s="281"/>
+      <c r="U56" s="282"/>
+      <c r="V56" s="282"/>
       <c r="W56" s="80"/>
-      <c r="X56" s="270"/>
-      <c r="Y56" s="270"/>
+      <c r="X56" s="268"/>
+      <c r="Y56" s="268"/>
       <c r="Z56" s="69"/>
-      <c r="AA56" s="288"/>
-      <c r="AB56" s="288"/>
-      <c r="AC56" s="289" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD56" s="273"/>
-      <c r="AE56" s="273"/>
-      <c r="AF56" s="273"/>
-      <c r="AG56" s="243"/>
-      <c r="AH56" s="243"/>
+      <c r="AA56" s="285"/>
+      <c r="AB56" s="285"/>
+      <c r="AC56" s="286" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD56" s="271"/>
+      <c r="AE56" s="271"/>
+      <c r="AF56" s="271"/>
+      <c r="AG56" s="241"/>
+      <c r="AH56" s="241"/>
       <c r="AI56" s="156"/>
       <c r="AJ56" s="156"/>
       <c r="AK56" s="156"/>
-      <c r="AL56" s="287"/>
-      <c r="AM56" s="287"/>
-      <c r="AO56" s="290" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP56" s="290"/>
-      <c r="AQ56" s="290"/>
-      <c r="AR56" s="290"/>
-      <c r="AS56" s="290"/>
-      <c r="AT56" s="291" t="n">
+      <c r="AL56" s="284"/>
+      <c r="AM56" s="284"/>
+      <c r="AO56" s="287" t="s">
+        <v>174</v>
+      </c>
+      <c r="AP56" s="287"/>
+      <c r="AQ56" s="287"/>
+      <c r="AR56" s="287"/>
+      <c r="AS56" s="287"/>
+      <c r="AT56" s="288" t="n">
         <f aca="false">IF(AT54="","",AT41-AT44-AT54)</f>
         <v>70</v>
       </c>
-      <c r="AU56" s="291"/>
-      <c r="AV56" s="291"/>
-      <c r="AW56" s="291"/>
-      <c r="AX56" s="292" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY56" s="292"/>
-      <c r="AZ56" s="293" t="n">
+      <c r="AU56" s="288"/>
+      <c r="AV56" s="288"/>
+      <c r="AW56" s="288"/>
+      <c r="AX56" s="289" t="s">
+        <v>38</v>
+      </c>
+      <c r="AY56" s="289"/>
+      <c r="AZ56" s="288" t="n">
         <f aca="false">IF(AZ54="","",AZ41-AZ44-AZ54)</f>
         <v>142</v>
       </c>
-      <c r="BA56" s="293"/>
-      <c r="BB56" s="293"/>
-      <c r="BC56" s="293"/>
+      <c r="BA56" s="288"/>
+      <c r="BB56" s="288"/>
+      <c r="BC56" s="288"/>
       <c r="BD56" s="178" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BE56" s="178"/>
       <c r="BF56" s="186" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="BG56" s="95"/>
       <c r="BH56" s="95"/>
@@ -7491,1021 +7476,1021 @@
       <c r="BR56" s="95"/>
       <c r="BS56" s="95"/>
       <c r="BT56" s="95"/>
-      <c r="BU56" s="294"/>
-      <c r="BV56" s="294"/>
-      <c r="BW56" s="294"/>
-      <c r="BX56" s="294"/>
-      <c r="BY56" s="294"/>
-      <c r="BZ56" s="294"/>
+      <c r="BU56" s="290"/>
+      <c r="BV56" s="290"/>
+      <c r="BW56" s="290"/>
+      <c r="BX56" s="290"/>
+      <c r="BY56" s="290"/>
+      <c r="BZ56" s="290"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="253" t="s">
-        <v>175</v>
-      </c>
-      <c r="C57" s="254" t="s">
+      <c r="B57" s="251" t="s">
         <v>176</v>
       </c>
-      <c r="D57" s="254"/>
-      <c r="E57" s="254"/>
-      <c r="F57" s="254"/>
-      <c r="G57" s="254"/>
-      <c r="H57" s="254"/>
-      <c r="I57" s="254"/>
-      <c r="J57" s="254"/>
-      <c r="K57" s="254"/>
-      <c r="L57" s="254"/>
-      <c r="M57" s="254"/>
-      <c r="N57" s="254"/>
-      <c r="O57" s="255" t="s">
+      <c r="C57" s="252" t="s">
         <v>177</v>
       </c>
-      <c r="P57" s="255"/>
-      <c r="Q57" s="255"/>
-      <c r="R57" s="255"/>
-      <c r="S57" s="255"/>
-      <c r="T57" s="255"/>
-      <c r="U57" s="256"/>
-      <c r="V57" s="256"/>
-      <c r="W57" s="257" t="n">
+      <c r="D57" s="252"/>
+      <c r="E57" s="252"/>
+      <c r="F57" s="252"/>
+      <c r="G57" s="252"/>
+      <c r="H57" s="252"/>
+      <c r="I57" s="252"/>
+      <c r="J57" s="252"/>
+      <c r="K57" s="252"/>
+      <c r="L57" s="252"/>
+      <c r="M57" s="252"/>
+      <c r="N57" s="252"/>
+      <c r="O57" s="253" t="s">
+        <v>178</v>
+      </c>
+      <c r="P57" s="253"/>
+      <c r="Q57" s="253"/>
+      <c r="R57" s="253"/>
+      <c r="S57" s="253"/>
+      <c r="T57" s="253"/>
+      <c r="U57" s="254"/>
+      <c r="V57" s="254"/>
+      <c r="W57" s="255" t="n">
         <v>70</v>
       </c>
-      <c r="X57" s="295"/>
-      <c r="Y57" s="295"/>
-      <c r="Z57" s="284" t="n">
+      <c r="X57" s="291"/>
+      <c r="Y57" s="291"/>
+      <c r="Z57" s="281" t="n">
         <v>80</v>
       </c>
-      <c r="AA57" s="265"/>
-      <c r="AB57" s="265"/>
-      <c r="AC57" s="260" t="n">
+      <c r="AA57" s="263"/>
+      <c r="AB57" s="263"/>
+      <c r="AC57" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="AD57" s="276"/>
-      <c r="AE57" s="276"/>
-      <c r="AF57" s="276"/>
-      <c r="AG57" s="296" t="n">
+      <c r="AD57" s="274"/>
+      <c r="AE57" s="274"/>
+      <c r="AF57" s="274"/>
+      <c r="AG57" s="292" t="n">
         <v>31</v>
       </c>
-      <c r="AH57" s="296"/>
-      <c r="AI57" s="297"/>
-      <c r="AJ57" s="297"/>
-      <c r="AK57" s="297"/>
-      <c r="AL57" s="298" t="n">
+      <c r="AH57" s="292"/>
+      <c r="AI57" s="293"/>
+      <c r="AJ57" s="293"/>
+      <c r="AK57" s="293"/>
+      <c r="AL57" s="294" t="n">
         <v>30</v>
       </c>
-      <c r="AM57" s="298"/>
-      <c r="AO57" s="290"/>
-      <c r="AP57" s="290"/>
-      <c r="AQ57" s="290"/>
-      <c r="AR57" s="290"/>
-      <c r="AS57" s="290"/>
-      <c r="AT57" s="291"/>
-      <c r="AU57" s="291"/>
-      <c r="AV57" s="291"/>
-      <c r="AW57" s="291"/>
-      <c r="AX57" s="292"/>
-      <c r="AY57" s="292"/>
-      <c r="AZ57" s="293"/>
-      <c r="BA57" s="293"/>
-      <c r="BB57" s="293"/>
-      <c r="BC57" s="293"/>
+      <c r="AM57" s="294"/>
+      <c r="AO57" s="287"/>
+      <c r="AP57" s="287"/>
+      <c r="AQ57" s="287"/>
+      <c r="AR57" s="287"/>
+      <c r="AS57" s="287"/>
+      <c r="AT57" s="288"/>
+      <c r="AU57" s="288"/>
+      <c r="AV57" s="288"/>
+      <c r="AW57" s="288"/>
+      <c r="AX57" s="289"/>
+      <c r="AY57" s="289"/>
+      <c r="AZ57" s="288"/>
+      <c r="BA57" s="288"/>
+      <c r="BB57" s="288"/>
+      <c r="BC57" s="288"/>
       <c r="BD57" s="178"/>
       <c r="BE57" s="178"/>
-      <c r="BF57" s="299"/>
-      <c r="BG57" s="299"/>
-      <c r="BH57" s="299"/>
-      <c r="BI57" s="299"/>
-      <c r="BJ57" s="299"/>
-      <c r="BK57" s="299"/>
-      <c r="BL57" s="299"/>
-      <c r="BM57" s="299"/>
-      <c r="BN57" s="299"/>
-      <c r="BO57" s="299"/>
-      <c r="BP57" s="299"/>
-      <c r="BQ57" s="299"/>
-      <c r="BR57" s="299"/>
-      <c r="BS57" s="299"/>
-      <c r="BT57" s="299"/>
-      <c r="BU57" s="299"/>
-      <c r="BV57" s="299"/>
-      <c r="BW57" s="299"/>
-      <c r="BX57" s="299"/>
-      <c r="BY57" s="299"/>
-      <c r="BZ57" s="299"/>
+      <c r="BF57" s="295"/>
+      <c r="BG57" s="295"/>
+      <c r="BH57" s="295"/>
+      <c r="BI57" s="295"/>
+      <c r="BJ57" s="295"/>
+      <c r="BK57" s="295"/>
+      <c r="BL57" s="295"/>
+      <c r="BM57" s="295"/>
+      <c r="BN57" s="295"/>
+      <c r="BO57" s="295"/>
+      <c r="BP57" s="295"/>
+      <c r="BQ57" s="295"/>
+      <c r="BR57" s="295"/>
+      <c r="BS57" s="295"/>
+      <c r="BT57" s="295"/>
+      <c r="BU57" s="295"/>
+      <c r="BV57" s="295"/>
+      <c r="BW57" s="295"/>
+      <c r="BX57" s="295"/>
+      <c r="BY57" s="295"/>
+      <c r="BZ57" s="295"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="253"/>
-      <c r="C58" s="264"/>
-      <c r="D58" s="264"/>
-      <c r="E58" s="264"/>
-      <c r="F58" s="264"/>
-      <c r="G58" s="264"/>
-      <c r="H58" s="264"/>
-      <c r="I58" s="264"/>
-      <c r="J58" s="264"/>
-      <c r="K58" s="264"/>
-      <c r="L58" s="264"/>
-      <c r="M58" s="264"/>
-      <c r="N58" s="264"/>
-      <c r="O58" s="255"/>
-      <c r="P58" s="255"/>
-      <c r="Q58" s="255"/>
-      <c r="R58" s="255"/>
-      <c r="S58" s="255"/>
-      <c r="T58" s="255"/>
-      <c r="U58" s="256"/>
-      <c r="V58" s="256"/>
-      <c r="W58" s="257"/>
-      <c r="X58" s="295"/>
-      <c r="Y58" s="295"/>
-      <c r="Z58" s="284"/>
-      <c r="AA58" s="265"/>
-      <c r="AB58" s="265"/>
-      <c r="AC58" s="241" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD58" s="276"/>
-      <c r="AE58" s="276"/>
-      <c r="AF58" s="276"/>
-      <c r="AG58" s="296"/>
-      <c r="AH58" s="296"/>
-      <c r="AI58" s="297"/>
-      <c r="AJ58" s="297"/>
-      <c r="AK58" s="297"/>
-      <c r="AL58" s="298"/>
-      <c r="AM58" s="298"/>
-      <c r="AO58" s="300" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP58" s="300"/>
-      <c r="AQ58" s="300"/>
-      <c r="AR58" s="300"/>
-      <c r="AS58" s="300"/>
-      <c r="AT58" s="291"/>
-      <c r="AU58" s="291"/>
-      <c r="AV58" s="291"/>
-      <c r="AW58" s="291"/>
-      <c r="AX58" s="292"/>
-      <c r="AY58" s="292"/>
-      <c r="AZ58" s="293"/>
-      <c r="BA58" s="293"/>
-      <c r="BB58" s="293"/>
-      <c r="BC58" s="293"/>
+      <c r="B58" s="251"/>
+      <c r="C58" s="262"/>
+      <c r="D58" s="262"/>
+      <c r="E58" s="262"/>
+      <c r="F58" s="262"/>
+      <c r="G58" s="262"/>
+      <c r="H58" s="262"/>
+      <c r="I58" s="262"/>
+      <c r="J58" s="262"/>
+      <c r="K58" s="262"/>
+      <c r="L58" s="262"/>
+      <c r="M58" s="262"/>
+      <c r="N58" s="262"/>
+      <c r="O58" s="253"/>
+      <c r="P58" s="253"/>
+      <c r="Q58" s="253"/>
+      <c r="R58" s="253"/>
+      <c r="S58" s="253"/>
+      <c r="T58" s="253"/>
+      <c r="U58" s="254"/>
+      <c r="V58" s="254"/>
+      <c r="W58" s="255"/>
+      <c r="X58" s="291"/>
+      <c r="Y58" s="291"/>
+      <c r="Z58" s="281"/>
+      <c r="AA58" s="263"/>
+      <c r="AB58" s="263"/>
+      <c r="AC58" s="239" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD58" s="274"/>
+      <c r="AE58" s="274"/>
+      <c r="AF58" s="274"/>
+      <c r="AG58" s="292"/>
+      <c r="AH58" s="292"/>
+      <c r="AI58" s="293"/>
+      <c r="AJ58" s="293"/>
+      <c r="AK58" s="293"/>
+      <c r="AL58" s="294"/>
+      <c r="AM58" s="294"/>
+      <c r="AO58" s="296" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP58" s="296"/>
+      <c r="AQ58" s="296"/>
+      <c r="AR58" s="296"/>
+      <c r="AS58" s="296"/>
+      <c r="AT58" s="288"/>
+      <c r="AU58" s="288"/>
+      <c r="AV58" s="288"/>
+      <c r="AW58" s="288"/>
+      <c r="AX58" s="289"/>
+      <c r="AY58" s="289"/>
+      <c r="AZ58" s="288"/>
+      <c r="BA58" s="288"/>
+      <c r="BB58" s="288"/>
+      <c r="BC58" s="288"/>
       <c r="BD58" s="178"/>
       <c r="BE58" s="178"/>
-      <c r="BF58" s="299"/>
-      <c r="BG58" s="299"/>
-      <c r="BH58" s="299"/>
-      <c r="BI58" s="299"/>
-      <c r="BJ58" s="299"/>
-      <c r="BK58" s="299"/>
-      <c r="BL58" s="299"/>
-      <c r="BM58" s="299"/>
-      <c r="BN58" s="299"/>
-      <c r="BO58" s="299"/>
-      <c r="BP58" s="299"/>
-      <c r="BQ58" s="299"/>
-      <c r="BR58" s="299"/>
-      <c r="BS58" s="299"/>
-      <c r="BT58" s="299"/>
-      <c r="BU58" s="299"/>
-      <c r="BV58" s="299"/>
-      <c r="BW58" s="299"/>
-      <c r="BX58" s="299"/>
-      <c r="BY58" s="299"/>
-      <c r="BZ58" s="299"/>
+      <c r="BF58" s="295"/>
+      <c r="BG58" s="295"/>
+      <c r="BH58" s="295"/>
+      <c r="BI58" s="295"/>
+      <c r="BJ58" s="295"/>
+      <c r="BK58" s="295"/>
+      <c r="BL58" s="295"/>
+      <c r="BM58" s="295"/>
+      <c r="BN58" s="295"/>
+      <c r="BO58" s="295"/>
+      <c r="BP58" s="295"/>
+      <c r="BQ58" s="295"/>
+      <c r="BR58" s="295"/>
+      <c r="BS58" s="295"/>
+      <c r="BT58" s="295"/>
+      <c r="BU58" s="295"/>
+      <c r="BV58" s="295"/>
+      <c r="BW58" s="295"/>
+      <c r="BX58" s="295"/>
+      <c r="BY58" s="295"/>
+      <c r="BZ58" s="295"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="253"/>
-      <c r="C59" s="266" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" s="266"/>
-      <c r="E59" s="266"/>
-      <c r="F59" s="266"/>
-      <c r="G59" s="266"/>
-      <c r="H59" s="266"/>
-      <c r="I59" s="266"/>
-      <c r="J59" s="266"/>
-      <c r="K59" s="266"/>
-      <c r="L59" s="266"/>
-      <c r="M59" s="266"/>
-      <c r="N59" s="266"/>
-      <c r="O59" s="267" t="s">
+      <c r="B59" s="251"/>
+      <c r="C59" s="264" t="s">
         <v>180</v>
       </c>
-      <c r="P59" s="267"/>
-      <c r="Q59" s="267"/>
-      <c r="R59" s="267"/>
-      <c r="S59" s="267"/>
-      <c r="T59" s="267"/>
-      <c r="U59" s="268"/>
-      <c r="V59" s="268"/>
-      <c r="W59" s="269" t="n">
+      <c r="D59" s="264"/>
+      <c r="E59" s="264"/>
+      <c r="F59" s="264"/>
+      <c r="G59" s="264"/>
+      <c r="H59" s="264"/>
+      <c r="I59" s="264"/>
+      <c r="J59" s="264"/>
+      <c r="K59" s="264"/>
+      <c r="L59" s="264"/>
+      <c r="M59" s="264"/>
+      <c r="N59" s="264"/>
+      <c r="O59" s="265" t="s">
+        <v>181</v>
+      </c>
+      <c r="P59" s="265"/>
+      <c r="Q59" s="265"/>
+      <c r="R59" s="265"/>
+      <c r="S59" s="265"/>
+      <c r="T59" s="265"/>
+      <c r="U59" s="266"/>
+      <c r="V59" s="266"/>
+      <c r="W59" s="267" t="n">
         <v>30</v>
       </c>
-      <c r="X59" s="270"/>
-      <c r="Y59" s="270"/>
-      <c r="Z59" s="269" t="n">
+      <c r="X59" s="268"/>
+      <c r="Y59" s="268"/>
+      <c r="Z59" s="267" t="n">
         <v>50</v>
       </c>
-      <c r="AA59" s="271"/>
-      <c r="AB59" s="271"/>
-      <c r="AC59" s="272" t="n">
+      <c r="AA59" s="269"/>
+      <c r="AB59" s="269"/>
+      <c r="AC59" s="270" t="n">
         <v>0</v>
       </c>
-      <c r="AD59" s="273"/>
-      <c r="AE59" s="273"/>
-      <c r="AF59" s="273"/>
-      <c r="AG59" s="274" t="n">
+      <c r="AD59" s="271"/>
+      <c r="AE59" s="271"/>
+      <c r="AF59" s="271"/>
+      <c r="AG59" s="272" t="n">
         <v>31</v>
       </c>
-      <c r="AH59" s="274"/>
+      <c r="AH59" s="272"/>
       <c r="AI59" s="156"/>
       <c r="AJ59" s="156"/>
       <c r="AK59" s="156"/>
-      <c r="AL59" s="275" t="n">
+      <c r="AL59" s="273" t="n">
         <v>30</v>
       </c>
-      <c r="AM59" s="275"/>
+      <c r="AM59" s="273"/>
       <c r="AO59" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP59" s="301"/>
-      <c r="AQ59" s="301"/>
-      <c r="AR59" s="301"/>
-      <c r="AS59" s="301"/>
-      <c r="AT59" s="301"/>
-      <c r="AU59" s="301"/>
-      <c r="AV59" s="301"/>
-      <c r="AW59" s="301"/>
-      <c r="AX59" s="301"/>
-      <c r="AY59" s="301"/>
-      <c r="AZ59" s="301"/>
-      <c r="BA59" s="301"/>
-      <c r="BB59" s="301"/>
-      <c r="BC59" s="301"/>
-      <c r="BD59" s="301"/>
-      <c r="BE59" s="301"/>
-      <c r="BF59" s="301"/>
-      <c r="BG59" s="301"/>
-      <c r="BH59" s="301"/>
-      <c r="BI59" s="301"/>
-      <c r="BJ59" s="301"/>
-      <c r="BK59" s="301"/>
-      <c r="BL59" s="301"/>
-      <c r="BM59" s="301"/>
-      <c r="BN59" s="301"/>
-      <c r="BO59" s="301"/>
-      <c r="BP59" s="301"/>
-      <c r="BQ59" s="301"/>
-      <c r="BR59" s="301"/>
-      <c r="BS59" s="301"/>
-      <c r="BT59" s="301"/>
-      <c r="BU59" s="301"/>
-      <c r="BV59" s="301"/>
-      <c r="BW59" s="301"/>
-      <c r="BX59" s="301"/>
-      <c r="BY59" s="301"/>
-      <c r="BZ59" s="301"/>
+        <v>182</v>
+      </c>
+      <c r="AP59" s="297"/>
+      <c r="AQ59" s="297"/>
+      <c r="AR59" s="297"/>
+      <c r="AS59" s="297"/>
+      <c r="AT59" s="297"/>
+      <c r="AU59" s="297"/>
+      <c r="AV59" s="297"/>
+      <c r="AW59" s="297"/>
+      <c r="AX59" s="297"/>
+      <c r="AY59" s="297"/>
+      <c r="AZ59" s="297"/>
+      <c r="BA59" s="297"/>
+      <c r="BB59" s="297"/>
+      <c r="BC59" s="297"/>
+      <c r="BD59" s="297"/>
+      <c r="BE59" s="297"/>
+      <c r="BF59" s="297"/>
+      <c r="BG59" s="297"/>
+      <c r="BH59" s="297"/>
+      <c r="BI59" s="297"/>
+      <c r="BJ59" s="297"/>
+      <c r="BK59" s="297"/>
+      <c r="BL59" s="297"/>
+      <c r="BM59" s="297"/>
+      <c r="BN59" s="297"/>
+      <c r="BO59" s="297"/>
+      <c r="BP59" s="297"/>
+      <c r="BQ59" s="297"/>
+      <c r="BR59" s="297"/>
+      <c r="BS59" s="297"/>
+      <c r="BT59" s="297"/>
+      <c r="BU59" s="297"/>
+      <c r="BV59" s="297"/>
+      <c r="BW59" s="297"/>
+      <c r="BX59" s="297"/>
+      <c r="BY59" s="297"/>
+      <c r="BZ59" s="297"/>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="253"/>
-      <c r="C60" s="264"/>
-      <c r="D60" s="264"/>
-      <c r="E60" s="264"/>
-      <c r="F60" s="264"/>
-      <c r="G60" s="264"/>
-      <c r="H60" s="264"/>
-      <c r="I60" s="264"/>
-      <c r="J60" s="264"/>
-      <c r="K60" s="264"/>
-      <c r="L60" s="264"/>
-      <c r="M60" s="264"/>
-      <c r="N60" s="264"/>
-      <c r="O60" s="267"/>
-      <c r="P60" s="267"/>
-      <c r="Q60" s="267"/>
-      <c r="R60" s="267"/>
-      <c r="S60" s="267"/>
-      <c r="T60" s="267"/>
-      <c r="U60" s="268"/>
-      <c r="V60" s="268"/>
-      <c r="W60" s="269"/>
-      <c r="X60" s="270"/>
-      <c r="Y60" s="270"/>
-      <c r="Z60" s="269"/>
-      <c r="AA60" s="276"/>
-      <c r="AB60" s="276"/>
-      <c r="AC60" s="277" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD60" s="273"/>
-      <c r="AE60" s="273"/>
-      <c r="AF60" s="273"/>
-      <c r="AG60" s="274"/>
-      <c r="AH60" s="274"/>
+      <c r="B60" s="251"/>
+      <c r="C60" s="262"/>
+      <c r="D60" s="262"/>
+      <c r="E60" s="262"/>
+      <c r="F60" s="262"/>
+      <c r="G60" s="262"/>
+      <c r="H60" s="262"/>
+      <c r="I60" s="262"/>
+      <c r="J60" s="262"/>
+      <c r="K60" s="262"/>
+      <c r="L60" s="262"/>
+      <c r="M60" s="262"/>
+      <c r="N60" s="262"/>
+      <c r="O60" s="265"/>
+      <c r="P60" s="265"/>
+      <c r="Q60" s="265"/>
+      <c r="R60" s="265"/>
+      <c r="S60" s="265"/>
+      <c r="T60" s="265"/>
+      <c r="U60" s="266"/>
+      <c r="V60" s="266"/>
+      <c r="W60" s="267"/>
+      <c r="X60" s="268"/>
+      <c r="Y60" s="268"/>
+      <c r="Z60" s="267"/>
+      <c r="AA60" s="274"/>
+      <c r="AB60" s="274"/>
+      <c r="AC60" s="275" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD60" s="271"/>
+      <c r="AE60" s="271"/>
+      <c r="AF60" s="271"/>
+      <c r="AG60" s="272"/>
+      <c r="AH60" s="272"/>
       <c r="AI60" s="156"/>
       <c r="AJ60" s="156"/>
       <c r="AK60" s="156"/>
-      <c r="AL60" s="275"/>
-      <c r="AM60" s="275"/>
-      <c r="AO60" s="302" t="s">
-        <v>182</v>
-      </c>
-      <c r="AP60" s="302"/>
-      <c r="AQ60" s="302"/>
-      <c r="AR60" s="302"/>
-      <c r="AS60" s="302"/>
-      <c r="AT60" s="302"/>
-      <c r="AU60" s="302"/>
-      <c r="AV60" s="302"/>
-      <c r="AW60" s="302"/>
-      <c r="AX60" s="302"/>
-      <c r="AY60" s="302"/>
-      <c r="AZ60" s="302"/>
-      <c r="BA60" s="302"/>
-      <c r="BB60" s="302"/>
-      <c r="BC60" s="302"/>
-      <c r="BD60" s="302"/>
-      <c r="BE60" s="302"/>
-      <c r="BF60" s="302"/>
-      <c r="BG60" s="302"/>
-      <c r="BH60" s="302"/>
-      <c r="BI60" s="302"/>
-      <c r="BJ60" s="302"/>
-      <c r="BK60" s="302"/>
-      <c r="BL60" s="302"/>
-      <c r="BM60" s="302"/>
-      <c r="BN60" s="302"/>
-      <c r="BO60" s="302"/>
-      <c r="BP60" s="302"/>
-      <c r="BQ60" s="302"/>
-      <c r="BR60" s="302"/>
-      <c r="BS60" s="302"/>
-      <c r="BT60" s="302"/>
-      <c r="BU60" s="302"/>
-      <c r="BV60" s="302"/>
-      <c r="BW60" s="302"/>
-      <c r="BX60" s="302"/>
-      <c r="BY60" s="302"/>
-      <c r="BZ60" s="302"/>
+      <c r="AL60" s="273"/>
+      <c r="AM60" s="273"/>
+      <c r="AO60" s="298" t="s">
+        <v>183</v>
+      </c>
+      <c r="AP60" s="298"/>
+      <c r="AQ60" s="298"/>
+      <c r="AR60" s="298"/>
+      <c r="AS60" s="298"/>
+      <c r="AT60" s="298"/>
+      <c r="AU60" s="298"/>
+      <c r="AV60" s="298"/>
+      <c r="AW60" s="298"/>
+      <c r="AX60" s="298"/>
+      <c r="AY60" s="298"/>
+      <c r="AZ60" s="298"/>
+      <c r="BA60" s="298"/>
+      <c r="BB60" s="298"/>
+      <c r="BC60" s="298"/>
+      <c r="BD60" s="298"/>
+      <c r="BE60" s="298"/>
+      <c r="BF60" s="298"/>
+      <c r="BG60" s="298"/>
+      <c r="BH60" s="298"/>
+      <c r="BI60" s="298"/>
+      <c r="BJ60" s="298"/>
+      <c r="BK60" s="298"/>
+      <c r="BL60" s="298"/>
+      <c r="BM60" s="298"/>
+      <c r="BN60" s="298"/>
+      <c r="BO60" s="298"/>
+      <c r="BP60" s="298"/>
+      <c r="BQ60" s="298"/>
+      <c r="BR60" s="298"/>
+      <c r="BS60" s="298"/>
+      <c r="BT60" s="298"/>
+      <c r="BU60" s="298"/>
+      <c r="BV60" s="298"/>
+      <c r="BW60" s="298"/>
+      <c r="BX60" s="298"/>
+      <c r="BY60" s="298"/>
+      <c r="BZ60" s="298"/>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="253"/>
-      <c r="C61" s="282"/>
-      <c r="D61" s="282"/>
-      <c r="E61" s="282"/>
-      <c r="F61" s="282"/>
-      <c r="G61" s="282"/>
-      <c r="H61" s="282"/>
-      <c r="I61" s="282"/>
-      <c r="J61" s="282"/>
-      <c r="K61" s="282"/>
-      <c r="L61" s="282"/>
-      <c r="M61" s="282"/>
-      <c r="N61" s="282"/>
-      <c r="O61" s="283" t="s">
-        <v>169</v>
-      </c>
-      <c r="P61" s="283"/>
+      <c r="B61" s="251"/>
+      <c r="C61" s="279"/>
+      <c r="D61" s="279"/>
+      <c r="E61" s="279"/>
+      <c r="F61" s="279"/>
+      <c r="G61" s="279"/>
+      <c r="H61" s="279"/>
+      <c r="I61" s="279"/>
+      <c r="J61" s="279"/>
+      <c r="K61" s="279"/>
+      <c r="L61" s="279"/>
+      <c r="M61" s="279"/>
+      <c r="N61" s="279"/>
+      <c r="O61" s="280" t="s">
+        <v>170</v>
+      </c>
+      <c r="P61" s="280"/>
       <c r="Q61" s="117"/>
       <c r="R61" s="117"/>
       <c r="S61" s="117"/>
-      <c r="T61" s="284" t="n">
+      <c r="T61" s="281" t="n">
         <v>1</v>
       </c>
-      <c r="U61" s="285"/>
-      <c r="V61" s="285"/>
+      <c r="U61" s="282"/>
+      <c r="V61" s="282"/>
       <c r="W61" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="X61" s="270"/>
-      <c r="Y61" s="270"/>
+        <v>171</v>
+      </c>
+      <c r="X61" s="268"/>
+      <c r="Y61" s="268"/>
       <c r="Z61" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA61" s="271"/>
-      <c r="AB61" s="271"/>
-      <c r="AC61" s="286" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD61" s="273"/>
-      <c r="AE61" s="273"/>
-      <c r="AF61" s="273"/>
-      <c r="AG61" s="243" t="s">
         <v>171</v>
       </c>
-      <c r="AH61" s="243"/>
+      <c r="AA61" s="269"/>
+      <c r="AB61" s="269"/>
+      <c r="AC61" s="283" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD61" s="271"/>
+      <c r="AE61" s="271"/>
+      <c r="AF61" s="271"/>
+      <c r="AG61" s="241" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH61" s="241"/>
       <c r="AI61" s="156"/>
       <c r="AJ61" s="156"/>
       <c r="AK61" s="156"/>
-      <c r="AL61" s="287" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM61" s="287"/>
-      <c r="AO61" s="302"/>
-      <c r="AP61" s="302"/>
-      <c r="AQ61" s="302"/>
-      <c r="AR61" s="302"/>
-      <c r="AS61" s="302"/>
-      <c r="AT61" s="302"/>
-      <c r="AU61" s="302"/>
-      <c r="AV61" s="302"/>
-      <c r="AW61" s="302"/>
-      <c r="AX61" s="302"/>
-      <c r="AY61" s="302"/>
-      <c r="AZ61" s="302"/>
-      <c r="BA61" s="302"/>
-      <c r="BB61" s="302"/>
-      <c r="BC61" s="302"/>
-      <c r="BD61" s="302"/>
-      <c r="BE61" s="302"/>
-      <c r="BF61" s="302"/>
-      <c r="BG61" s="302"/>
-      <c r="BH61" s="302"/>
-      <c r="BI61" s="302"/>
-      <c r="BJ61" s="302"/>
-      <c r="BK61" s="302"/>
-      <c r="BL61" s="302"/>
-      <c r="BM61" s="302"/>
-      <c r="BN61" s="302"/>
-      <c r="BO61" s="302"/>
-      <c r="BP61" s="302"/>
-      <c r="BQ61" s="302"/>
-      <c r="BR61" s="302"/>
-      <c r="BS61" s="302"/>
-      <c r="BT61" s="302"/>
-      <c r="BU61" s="302"/>
-      <c r="BV61" s="302"/>
-      <c r="BW61" s="302"/>
-      <c r="BX61" s="302"/>
-      <c r="BY61" s="302"/>
-      <c r="BZ61" s="302"/>
+      <c r="AL61" s="284" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM61" s="284"/>
+      <c r="AO61" s="298"/>
+      <c r="AP61" s="298"/>
+      <c r="AQ61" s="298"/>
+      <c r="AR61" s="298"/>
+      <c r="AS61" s="298"/>
+      <c r="AT61" s="298"/>
+      <c r="AU61" s="298"/>
+      <c r="AV61" s="298"/>
+      <c r="AW61" s="298"/>
+      <c r="AX61" s="298"/>
+      <c r="AY61" s="298"/>
+      <c r="AZ61" s="298"/>
+      <c r="BA61" s="298"/>
+      <c r="BB61" s="298"/>
+      <c r="BC61" s="298"/>
+      <c r="BD61" s="298"/>
+      <c r="BE61" s="298"/>
+      <c r="BF61" s="298"/>
+      <c r="BG61" s="298"/>
+      <c r="BH61" s="298"/>
+      <c r="BI61" s="298"/>
+      <c r="BJ61" s="298"/>
+      <c r="BK61" s="298"/>
+      <c r="BL61" s="298"/>
+      <c r="BM61" s="298"/>
+      <c r="BN61" s="298"/>
+      <c r="BO61" s="298"/>
+      <c r="BP61" s="298"/>
+      <c r="BQ61" s="298"/>
+      <c r="BR61" s="298"/>
+      <c r="BS61" s="298"/>
+      <c r="BT61" s="298"/>
+      <c r="BU61" s="298"/>
+      <c r="BV61" s="298"/>
+      <c r="BW61" s="298"/>
+      <c r="BX61" s="298"/>
+      <c r="BY61" s="298"/>
+      <c r="BZ61" s="298"/>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="253"/>
-      <c r="C62" s="282"/>
-      <c r="D62" s="282"/>
-      <c r="E62" s="282"/>
-      <c r="F62" s="282"/>
-      <c r="G62" s="282"/>
-      <c r="H62" s="282"/>
-      <c r="I62" s="282"/>
-      <c r="J62" s="282"/>
-      <c r="K62" s="282"/>
-      <c r="L62" s="282"/>
-      <c r="M62" s="282"/>
-      <c r="N62" s="282"/>
-      <c r="O62" s="283"/>
-      <c r="P62" s="283"/>
+      <c r="B62" s="251"/>
+      <c r="C62" s="279"/>
+      <c r="D62" s="279"/>
+      <c r="E62" s="279"/>
+      <c r="F62" s="279"/>
+      <c r="G62" s="279"/>
+      <c r="H62" s="279"/>
+      <c r="I62" s="279"/>
+      <c r="J62" s="279"/>
+      <c r="K62" s="279"/>
+      <c r="L62" s="279"/>
+      <c r="M62" s="279"/>
+      <c r="N62" s="279"/>
+      <c r="O62" s="280"/>
+      <c r="P62" s="280"/>
       <c r="Q62" s="117"/>
       <c r="R62" s="117"/>
       <c r="S62" s="117"/>
-      <c r="T62" s="284"/>
-      <c r="U62" s="285"/>
-      <c r="V62" s="285"/>
+      <c r="T62" s="281"/>
+      <c r="U62" s="282"/>
+      <c r="V62" s="282"/>
       <c r="W62" s="80"/>
-      <c r="X62" s="270"/>
-      <c r="Y62" s="270"/>
+      <c r="X62" s="268"/>
+      <c r="Y62" s="268"/>
       <c r="Z62" s="69"/>
-      <c r="AA62" s="288"/>
-      <c r="AB62" s="288"/>
-      <c r="AC62" s="289" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD62" s="273"/>
-      <c r="AE62" s="273"/>
-      <c r="AF62" s="273"/>
-      <c r="AG62" s="243"/>
-      <c r="AH62" s="243"/>
+      <c r="AA62" s="285"/>
+      <c r="AB62" s="285"/>
+      <c r="AC62" s="286" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD62" s="271"/>
+      <c r="AE62" s="271"/>
+      <c r="AF62" s="271"/>
+      <c r="AG62" s="241"/>
+      <c r="AH62" s="241"/>
       <c r="AI62" s="156"/>
       <c r="AJ62" s="156"/>
       <c r="AK62" s="156"/>
-      <c r="AL62" s="287"/>
-      <c r="AM62" s="287"/>
-      <c r="AO62" s="302"/>
-      <c r="AP62" s="302"/>
-      <c r="AQ62" s="302"/>
-      <c r="AR62" s="302"/>
-      <c r="AS62" s="302"/>
-      <c r="AT62" s="302"/>
-      <c r="AU62" s="302"/>
-      <c r="AV62" s="302"/>
-      <c r="AW62" s="302"/>
-      <c r="AX62" s="302"/>
-      <c r="AY62" s="302"/>
-      <c r="AZ62" s="302"/>
-      <c r="BA62" s="302"/>
-      <c r="BB62" s="302"/>
-      <c r="BC62" s="302"/>
-      <c r="BD62" s="302"/>
-      <c r="BE62" s="302"/>
-      <c r="BF62" s="302"/>
-      <c r="BG62" s="302"/>
-      <c r="BH62" s="302"/>
-      <c r="BI62" s="302"/>
-      <c r="BJ62" s="302"/>
-      <c r="BK62" s="302"/>
-      <c r="BL62" s="302"/>
-      <c r="BM62" s="302"/>
-      <c r="BN62" s="302"/>
-      <c r="BO62" s="302"/>
-      <c r="BP62" s="302"/>
-      <c r="BQ62" s="302"/>
-      <c r="BR62" s="302"/>
-      <c r="BS62" s="302"/>
-      <c r="BT62" s="302"/>
-      <c r="BU62" s="302"/>
-      <c r="BV62" s="302"/>
-      <c r="BW62" s="302"/>
-      <c r="BX62" s="302"/>
-      <c r="BY62" s="302"/>
-      <c r="BZ62" s="302"/>
+      <c r="AL62" s="284"/>
+      <c r="AM62" s="284"/>
+      <c r="AO62" s="298"/>
+      <c r="AP62" s="298"/>
+      <c r="AQ62" s="298"/>
+      <c r="AR62" s="298"/>
+      <c r="AS62" s="298"/>
+      <c r="AT62" s="298"/>
+      <c r="AU62" s="298"/>
+      <c r="AV62" s="298"/>
+      <c r="AW62" s="298"/>
+      <c r="AX62" s="298"/>
+      <c r="AY62" s="298"/>
+      <c r="AZ62" s="298"/>
+      <c r="BA62" s="298"/>
+      <c r="BB62" s="298"/>
+      <c r="BC62" s="298"/>
+      <c r="BD62" s="298"/>
+      <c r="BE62" s="298"/>
+      <c r="BF62" s="298"/>
+      <c r="BG62" s="298"/>
+      <c r="BH62" s="298"/>
+      <c r="BI62" s="298"/>
+      <c r="BJ62" s="298"/>
+      <c r="BK62" s="298"/>
+      <c r="BL62" s="298"/>
+      <c r="BM62" s="298"/>
+      <c r="BN62" s="298"/>
+      <c r="BO62" s="298"/>
+      <c r="BP62" s="298"/>
+      <c r="BQ62" s="298"/>
+      <c r="BR62" s="298"/>
+      <c r="BS62" s="298"/>
+      <c r="BT62" s="298"/>
+      <c r="BU62" s="298"/>
+      <c r="BV62" s="298"/>
+      <c r="BW62" s="298"/>
+      <c r="BX62" s="298"/>
+      <c r="BY62" s="298"/>
+      <c r="BZ62" s="298"/>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="253" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="254" t="s">
+      <c r="B63" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="254"/>
-      <c r="E63" s="254"/>
-      <c r="F63" s="254"/>
-      <c r="G63" s="254"/>
-      <c r="H63" s="254"/>
-      <c r="I63" s="254"/>
-      <c r="J63" s="254"/>
-      <c r="K63" s="254"/>
-      <c r="L63" s="254"/>
-      <c r="M63" s="254"/>
-      <c r="N63" s="254"/>
-      <c r="O63" s="303" t="s">
-        <v>165</v>
-      </c>
-      <c r="P63" s="303"/>
-      <c r="Q63" s="303"/>
-      <c r="R63" s="303"/>
-      <c r="S63" s="303"/>
-      <c r="T63" s="303"/>
-      <c r="U63" s="256"/>
-      <c r="V63" s="256"/>
-      <c r="W63" s="257" t="n">
+      <c r="C63" s="252" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="252"/>
+      <c r="E63" s="252"/>
+      <c r="F63" s="252"/>
+      <c r="G63" s="252"/>
+      <c r="H63" s="252"/>
+      <c r="I63" s="252"/>
+      <c r="J63" s="252"/>
+      <c r="K63" s="252"/>
+      <c r="L63" s="252"/>
+      <c r="M63" s="252"/>
+      <c r="N63" s="252"/>
+      <c r="O63" s="299" t="s">
+        <v>166</v>
+      </c>
+      <c r="P63" s="299"/>
+      <c r="Q63" s="299"/>
+      <c r="R63" s="299"/>
+      <c r="S63" s="299"/>
+      <c r="T63" s="299"/>
+      <c r="U63" s="254"/>
+      <c r="V63" s="254"/>
+      <c r="W63" s="255" t="n">
         <v>100</v>
       </c>
-      <c r="X63" s="295"/>
-      <c r="Y63" s="295"/>
-      <c r="Z63" s="284" t="n">
+      <c r="X63" s="291"/>
+      <c r="Y63" s="291"/>
+      <c r="Z63" s="281" t="n">
         <v>100</v>
       </c>
-      <c r="AA63" s="259"/>
-      <c r="AB63" s="259"/>
-      <c r="AC63" s="304" t="n">
+      <c r="AA63" s="257"/>
+      <c r="AB63" s="257"/>
+      <c r="AC63" s="300" t="n">
         <v>0</v>
       </c>
-      <c r="AD63" s="261"/>
-      <c r="AE63" s="261"/>
-      <c r="AF63" s="261"/>
-      <c r="AG63" s="262" t="n">
+      <c r="AD63" s="259"/>
+      <c r="AE63" s="259"/>
+      <c r="AF63" s="259"/>
+      <c r="AG63" s="260" t="n">
         <v>31</v>
       </c>
-      <c r="AH63" s="262"/>
+      <c r="AH63" s="260"/>
       <c r="AI63" s="148"/>
       <c r="AJ63" s="148"/>
       <c r="AK63" s="148"/>
-      <c r="AL63" s="263" t="n">
+      <c r="AL63" s="261" t="n">
         <v>30</v>
       </c>
-      <c r="AM63" s="263"/>
-      <c r="AO63" s="302"/>
-      <c r="AP63" s="302"/>
-      <c r="AQ63" s="302"/>
-      <c r="AR63" s="302"/>
-      <c r="AS63" s="302"/>
-      <c r="AT63" s="302"/>
-      <c r="AU63" s="302"/>
-      <c r="AV63" s="302"/>
-      <c r="AW63" s="302"/>
-      <c r="AX63" s="302"/>
-      <c r="AY63" s="302"/>
-      <c r="AZ63" s="302"/>
-      <c r="BA63" s="302"/>
-      <c r="BB63" s="302"/>
-      <c r="BC63" s="302"/>
-      <c r="BD63" s="302"/>
-      <c r="BE63" s="302"/>
-      <c r="BF63" s="302"/>
-      <c r="BG63" s="302"/>
-      <c r="BH63" s="302"/>
-      <c r="BI63" s="302"/>
-      <c r="BJ63" s="302"/>
-      <c r="BK63" s="302"/>
-      <c r="BL63" s="302"/>
-      <c r="BM63" s="302"/>
-      <c r="BN63" s="302"/>
-      <c r="BO63" s="302"/>
-      <c r="BP63" s="302"/>
-      <c r="BQ63" s="302"/>
-      <c r="BR63" s="302"/>
-      <c r="BS63" s="302"/>
-      <c r="BT63" s="302"/>
-      <c r="BU63" s="302"/>
-      <c r="BV63" s="302"/>
-      <c r="BW63" s="302"/>
-      <c r="BX63" s="302"/>
-      <c r="BY63" s="302"/>
-      <c r="BZ63" s="302"/>
+      <c r="AM63" s="261"/>
+      <c r="AO63" s="298"/>
+      <c r="AP63" s="298"/>
+      <c r="AQ63" s="298"/>
+      <c r="AR63" s="298"/>
+      <c r="AS63" s="298"/>
+      <c r="AT63" s="298"/>
+      <c r="AU63" s="298"/>
+      <c r="AV63" s="298"/>
+      <c r="AW63" s="298"/>
+      <c r="AX63" s="298"/>
+      <c r="AY63" s="298"/>
+      <c r="AZ63" s="298"/>
+      <c r="BA63" s="298"/>
+      <c r="BB63" s="298"/>
+      <c r="BC63" s="298"/>
+      <c r="BD63" s="298"/>
+      <c r="BE63" s="298"/>
+      <c r="BF63" s="298"/>
+      <c r="BG63" s="298"/>
+      <c r="BH63" s="298"/>
+      <c r="BI63" s="298"/>
+      <c r="BJ63" s="298"/>
+      <c r="BK63" s="298"/>
+      <c r="BL63" s="298"/>
+      <c r="BM63" s="298"/>
+      <c r="BN63" s="298"/>
+      <c r="BO63" s="298"/>
+      <c r="BP63" s="298"/>
+      <c r="BQ63" s="298"/>
+      <c r="BR63" s="298"/>
+      <c r="BS63" s="298"/>
+      <c r="BT63" s="298"/>
+      <c r="BU63" s="298"/>
+      <c r="BV63" s="298"/>
+      <c r="BW63" s="298"/>
+      <c r="BX63" s="298"/>
+      <c r="BY63" s="298"/>
+      <c r="BZ63" s="298"/>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="253"/>
-      <c r="C64" s="264"/>
-      <c r="D64" s="264"/>
-      <c r="E64" s="264"/>
-      <c r="F64" s="264"/>
-      <c r="G64" s="264"/>
-      <c r="H64" s="264"/>
-      <c r="I64" s="264"/>
-      <c r="J64" s="264"/>
-      <c r="K64" s="264"/>
-      <c r="L64" s="264"/>
-      <c r="M64" s="264"/>
-      <c r="N64" s="264"/>
-      <c r="O64" s="303"/>
-      <c r="P64" s="303"/>
-      <c r="Q64" s="303"/>
-      <c r="R64" s="303"/>
-      <c r="S64" s="303"/>
-      <c r="T64" s="303"/>
-      <c r="U64" s="256"/>
-      <c r="V64" s="256"/>
-      <c r="W64" s="257"/>
-      <c r="X64" s="295"/>
-      <c r="Y64" s="295"/>
-      <c r="Z64" s="284"/>
-      <c r="AA64" s="276"/>
-      <c r="AB64" s="276"/>
-      <c r="AC64" s="277" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD64" s="261"/>
-      <c r="AE64" s="261"/>
-      <c r="AF64" s="261"/>
-      <c r="AG64" s="262"/>
-      <c r="AH64" s="262"/>
+      <c r="B64" s="251"/>
+      <c r="C64" s="262"/>
+      <c r="D64" s="262"/>
+      <c r="E64" s="262"/>
+      <c r="F64" s="262"/>
+      <c r="G64" s="262"/>
+      <c r="H64" s="262"/>
+      <c r="I64" s="262"/>
+      <c r="J64" s="262"/>
+      <c r="K64" s="262"/>
+      <c r="L64" s="262"/>
+      <c r="M64" s="262"/>
+      <c r="N64" s="262"/>
+      <c r="O64" s="299"/>
+      <c r="P64" s="299"/>
+      <c r="Q64" s="299"/>
+      <c r="R64" s="299"/>
+      <c r="S64" s="299"/>
+      <c r="T64" s="299"/>
+      <c r="U64" s="254"/>
+      <c r="V64" s="254"/>
+      <c r="W64" s="255"/>
+      <c r="X64" s="291"/>
+      <c r="Y64" s="291"/>
+      <c r="Z64" s="281"/>
+      <c r="AA64" s="274"/>
+      <c r="AB64" s="274"/>
+      <c r="AC64" s="275" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD64" s="259"/>
+      <c r="AE64" s="259"/>
+      <c r="AF64" s="259"/>
+      <c r="AG64" s="260"/>
+      <c r="AH64" s="260"/>
       <c r="AI64" s="148"/>
       <c r="AJ64" s="148"/>
       <c r="AK64" s="148"/>
-      <c r="AL64" s="263"/>
-      <c r="AM64" s="263"/>
-      <c r="AO64" s="302"/>
-      <c r="AP64" s="302"/>
-      <c r="AQ64" s="302"/>
-      <c r="AR64" s="302"/>
-      <c r="AS64" s="302"/>
-      <c r="AT64" s="302"/>
-      <c r="AU64" s="302"/>
-      <c r="AV64" s="302"/>
-      <c r="AW64" s="302"/>
-      <c r="AX64" s="302"/>
-      <c r="AY64" s="302"/>
-      <c r="AZ64" s="302"/>
-      <c r="BA64" s="302"/>
-      <c r="BB64" s="302"/>
-      <c r="BC64" s="302"/>
-      <c r="BD64" s="302"/>
-      <c r="BE64" s="302"/>
-      <c r="BF64" s="302"/>
-      <c r="BG64" s="302"/>
-      <c r="BH64" s="302"/>
-      <c r="BI64" s="302"/>
-      <c r="BJ64" s="302"/>
-      <c r="BK64" s="302"/>
-      <c r="BL64" s="302"/>
-      <c r="BM64" s="302"/>
-      <c r="BN64" s="302"/>
-      <c r="BO64" s="302"/>
-      <c r="BP64" s="302"/>
-      <c r="BQ64" s="302"/>
-      <c r="BR64" s="302"/>
-      <c r="BS64" s="302"/>
-      <c r="BT64" s="302"/>
-      <c r="BU64" s="302"/>
-      <c r="BV64" s="302"/>
-      <c r="BW64" s="302"/>
-      <c r="BX64" s="302"/>
-      <c r="BY64" s="302"/>
-      <c r="BZ64" s="302"/>
+      <c r="AL64" s="261"/>
+      <c r="AM64" s="261"/>
+      <c r="AO64" s="298"/>
+      <c r="AP64" s="298"/>
+      <c r="AQ64" s="298"/>
+      <c r="AR64" s="298"/>
+      <c r="AS64" s="298"/>
+      <c r="AT64" s="298"/>
+      <c r="AU64" s="298"/>
+      <c r="AV64" s="298"/>
+      <c r="AW64" s="298"/>
+      <c r="AX64" s="298"/>
+      <c r="AY64" s="298"/>
+      <c r="AZ64" s="298"/>
+      <c r="BA64" s="298"/>
+      <c r="BB64" s="298"/>
+      <c r="BC64" s="298"/>
+      <c r="BD64" s="298"/>
+      <c r="BE64" s="298"/>
+      <c r="BF64" s="298"/>
+      <c r="BG64" s="298"/>
+      <c r="BH64" s="298"/>
+      <c r="BI64" s="298"/>
+      <c r="BJ64" s="298"/>
+      <c r="BK64" s="298"/>
+      <c r="BL64" s="298"/>
+      <c r="BM64" s="298"/>
+      <c r="BN64" s="298"/>
+      <c r="BO64" s="298"/>
+      <c r="BP64" s="298"/>
+      <c r="BQ64" s="298"/>
+      <c r="BR64" s="298"/>
+      <c r="BS64" s="298"/>
+      <c r="BT64" s="298"/>
+      <c r="BU64" s="298"/>
+      <c r="BV64" s="298"/>
+      <c r="BW64" s="298"/>
+      <c r="BX64" s="298"/>
+      <c r="BY64" s="298"/>
+      <c r="BZ64" s="298"/>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="253"/>
-      <c r="C65" s="282"/>
-      <c r="D65" s="282"/>
-      <c r="E65" s="282"/>
-      <c r="F65" s="282"/>
-      <c r="G65" s="282"/>
-      <c r="H65" s="282"/>
-      <c r="I65" s="282"/>
-      <c r="J65" s="282"/>
-      <c r="K65" s="282"/>
-      <c r="L65" s="282"/>
-      <c r="M65" s="282"/>
-      <c r="N65" s="282"/>
-      <c r="O65" s="283" t="s">
-        <v>186</v>
-      </c>
-      <c r="P65" s="283"/>
+      <c r="B65" s="251"/>
+      <c r="C65" s="279"/>
+      <c r="D65" s="279"/>
+      <c r="E65" s="279"/>
+      <c r="F65" s="279"/>
+      <c r="G65" s="279"/>
+      <c r="H65" s="279"/>
+      <c r="I65" s="279"/>
+      <c r="J65" s="279"/>
+      <c r="K65" s="279"/>
+      <c r="L65" s="279"/>
+      <c r="M65" s="279"/>
+      <c r="N65" s="279"/>
+      <c r="O65" s="280" t="s">
+        <v>187</v>
+      </c>
+      <c r="P65" s="280"/>
       <c r="Q65" s="117"/>
       <c r="R65" s="117"/>
       <c r="S65" s="117"/>
-      <c r="T65" s="284" t="n">
+      <c r="T65" s="281" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="285"/>
-      <c r="V65" s="285"/>
+      <c r="U65" s="282"/>
+      <c r="V65" s="282"/>
       <c r="W65" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="X65" s="270"/>
-      <c r="Y65" s="270"/>
+        <v>171</v>
+      </c>
+      <c r="X65" s="268"/>
+      <c r="Y65" s="268"/>
       <c r="Z65" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA65" s="265"/>
-      <c r="AB65" s="265"/>
-      <c r="AC65" s="305" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD65" s="276"/>
-      <c r="AE65" s="276"/>
-      <c r="AF65" s="276"/>
-      <c r="AG65" s="306" t="s">
         <v>171</v>
       </c>
-      <c r="AH65" s="306"/>
-      <c r="AI65" s="297"/>
-      <c r="AJ65" s="297"/>
-      <c r="AK65" s="297"/>
-      <c r="AL65" s="307" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM65" s="307"/>
-      <c r="AO65" s="302"/>
-      <c r="AP65" s="302"/>
-      <c r="AQ65" s="302"/>
-      <c r="AR65" s="302"/>
-      <c r="AS65" s="302"/>
-      <c r="AT65" s="302"/>
-      <c r="AU65" s="302"/>
-      <c r="AV65" s="302"/>
-      <c r="AW65" s="302"/>
-      <c r="AX65" s="302"/>
-      <c r="AY65" s="302"/>
-      <c r="AZ65" s="302"/>
-      <c r="BA65" s="302"/>
-      <c r="BB65" s="302"/>
-      <c r="BC65" s="302"/>
-      <c r="BD65" s="302"/>
-      <c r="BE65" s="302"/>
-      <c r="BF65" s="302"/>
-      <c r="BG65" s="302"/>
-      <c r="BH65" s="302"/>
-      <c r="BI65" s="302"/>
-      <c r="BJ65" s="302"/>
-      <c r="BK65" s="302"/>
-      <c r="BL65" s="302"/>
-      <c r="BM65" s="302"/>
-      <c r="BN65" s="302"/>
-      <c r="BO65" s="302"/>
-      <c r="BP65" s="302"/>
-      <c r="BQ65" s="302"/>
-      <c r="BR65" s="302"/>
-      <c r="BS65" s="302"/>
-      <c r="BT65" s="302"/>
-      <c r="BU65" s="302"/>
-      <c r="BV65" s="302"/>
-      <c r="BW65" s="302"/>
-      <c r="BX65" s="302"/>
-      <c r="BY65" s="302"/>
-      <c r="BZ65" s="302"/>
+      <c r="AA65" s="263"/>
+      <c r="AB65" s="263"/>
+      <c r="AC65" s="301" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD65" s="274"/>
+      <c r="AE65" s="274"/>
+      <c r="AF65" s="274"/>
+      <c r="AG65" s="302" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH65" s="302"/>
+      <c r="AI65" s="293"/>
+      <c r="AJ65" s="293"/>
+      <c r="AK65" s="293"/>
+      <c r="AL65" s="303" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM65" s="303"/>
+      <c r="AO65" s="298"/>
+      <c r="AP65" s="298"/>
+      <c r="AQ65" s="298"/>
+      <c r="AR65" s="298"/>
+      <c r="AS65" s="298"/>
+      <c r="AT65" s="298"/>
+      <c r="AU65" s="298"/>
+      <c r="AV65" s="298"/>
+      <c r="AW65" s="298"/>
+      <c r="AX65" s="298"/>
+      <c r="AY65" s="298"/>
+      <c r="AZ65" s="298"/>
+      <c r="BA65" s="298"/>
+      <c r="BB65" s="298"/>
+      <c r="BC65" s="298"/>
+      <c r="BD65" s="298"/>
+      <c r="BE65" s="298"/>
+      <c r="BF65" s="298"/>
+      <c r="BG65" s="298"/>
+      <c r="BH65" s="298"/>
+      <c r="BI65" s="298"/>
+      <c r="BJ65" s="298"/>
+      <c r="BK65" s="298"/>
+      <c r="BL65" s="298"/>
+      <c r="BM65" s="298"/>
+      <c r="BN65" s="298"/>
+      <c r="BO65" s="298"/>
+      <c r="BP65" s="298"/>
+      <c r="BQ65" s="298"/>
+      <c r="BR65" s="298"/>
+      <c r="BS65" s="298"/>
+      <c r="BT65" s="298"/>
+      <c r="BU65" s="298"/>
+      <c r="BV65" s="298"/>
+      <c r="BW65" s="298"/>
+      <c r="BX65" s="298"/>
+      <c r="BY65" s="298"/>
+      <c r="BZ65" s="298"/>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B66" s="253"/>
-      <c r="C66" s="282"/>
-      <c r="D66" s="282"/>
-      <c r="E66" s="282"/>
-      <c r="F66" s="282"/>
-      <c r="G66" s="282"/>
-      <c r="H66" s="282"/>
-      <c r="I66" s="282"/>
-      <c r="J66" s="282"/>
-      <c r="K66" s="282"/>
-      <c r="L66" s="282"/>
-      <c r="M66" s="282"/>
-      <c r="N66" s="282"/>
-      <c r="O66" s="283"/>
-      <c r="P66" s="283"/>
+      <c r="B66" s="251"/>
+      <c r="C66" s="279"/>
+      <c r="D66" s="279"/>
+      <c r="E66" s="279"/>
+      <c r="F66" s="279"/>
+      <c r="G66" s="279"/>
+      <c r="H66" s="279"/>
+      <c r="I66" s="279"/>
+      <c r="J66" s="279"/>
+      <c r="K66" s="279"/>
+      <c r="L66" s="279"/>
+      <c r="M66" s="279"/>
+      <c r="N66" s="279"/>
+      <c r="O66" s="280"/>
+      <c r="P66" s="280"/>
       <c r="Q66" s="117"/>
       <c r="R66" s="117"/>
       <c r="S66" s="117"/>
-      <c r="T66" s="284"/>
-      <c r="U66" s="285"/>
-      <c r="V66" s="285"/>
+      <c r="T66" s="281"/>
+      <c r="U66" s="282"/>
+      <c r="V66" s="282"/>
       <c r="W66" s="80"/>
-      <c r="X66" s="270"/>
-      <c r="Y66" s="270"/>
+      <c r="X66" s="268"/>
+      <c r="Y66" s="268"/>
       <c r="Z66" s="69"/>
-      <c r="AA66" s="276"/>
-      <c r="AB66" s="276"/>
-      <c r="AC66" s="277" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD66" s="276"/>
-      <c r="AE66" s="276"/>
-      <c r="AF66" s="276"/>
-      <c r="AG66" s="306"/>
-      <c r="AH66" s="306"/>
-      <c r="AI66" s="297"/>
-      <c r="AJ66" s="297"/>
-      <c r="AK66" s="297"/>
-      <c r="AL66" s="307"/>
-      <c r="AM66" s="307"/>
-      <c r="AO66" s="302"/>
-      <c r="AP66" s="302"/>
-      <c r="AQ66" s="302"/>
-      <c r="AR66" s="302"/>
-      <c r="AS66" s="302"/>
-      <c r="AT66" s="302"/>
-      <c r="AU66" s="302"/>
-      <c r="AV66" s="302"/>
-      <c r="AW66" s="302"/>
-      <c r="AX66" s="302"/>
-      <c r="AY66" s="302"/>
-      <c r="AZ66" s="302"/>
-      <c r="BA66" s="302"/>
-      <c r="BB66" s="302"/>
-      <c r="BC66" s="302"/>
-      <c r="BD66" s="302"/>
-      <c r="BE66" s="302"/>
-      <c r="BF66" s="302"/>
-      <c r="BG66" s="302"/>
-      <c r="BH66" s="302"/>
-      <c r="BI66" s="302"/>
-      <c r="BJ66" s="302"/>
-      <c r="BK66" s="302"/>
-      <c r="BL66" s="302"/>
-      <c r="BM66" s="302"/>
-      <c r="BN66" s="302"/>
-      <c r="BO66" s="302"/>
-      <c r="BP66" s="302"/>
-      <c r="BQ66" s="302"/>
-      <c r="BR66" s="302"/>
-      <c r="BS66" s="302"/>
-      <c r="BT66" s="302"/>
-      <c r="BU66" s="302"/>
-      <c r="BV66" s="302"/>
-      <c r="BW66" s="302"/>
-      <c r="BX66" s="302"/>
-      <c r="BY66" s="302"/>
-      <c r="BZ66" s="302"/>
+      <c r="AA66" s="274"/>
+      <c r="AB66" s="274"/>
+      <c r="AC66" s="275" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD66" s="274"/>
+      <c r="AE66" s="274"/>
+      <c r="AF66" s="274"/>
+      <c r="AG66" s="302"/>
+      <c r="AH66" s="302"/>
+      <c r="AI66" s="293"/>
+      <c r="AJ66" s="293"/>
+      <c r="AK66" s="293"/>
+      <c r="AL66" s="303"/>
+      <c r="AM66" s="303"/>
+      <c r="AO66" s="298"/>
+      <c r="AP66" s="298"/>
+      <c r="AQ66" s="298"/>
+      <c r="AR66" s="298"/>
+      <c r="AS66" s="298"/>
+      <c r="AT66" s="298"/>
+      <c r="AU66" s="298"/>
+      <c r="AV66" s="298"/>
+      <c r="AW66" s="298"/>
+      <c r="AX66" s="298"/>
+      <c r="AY66" s="298"/>
+      <c r="AZ66" s="298"/>
+      <c r="BA66" s="298"/>
+      <c r="BB66" s="298"/>
+      <c r="BC66" s="298"/>
+      <c r="BD66" s="298"/>
+      <c r="BE66" s="298"/>
+      <c r="BF66" s="298"/>
+      <c r="BG66" s="298"/>
+      <c r="BH66" s="298"/>
+      <c r="BI66" s="298"/>
+      <c r="BJ66" s="298"/>
+      <c r="BK66" s="298"/>
+      <c r="BL66" s="298"/>
+      <c r="BM66" s="298"/>
+      <c r="BN66" s="298"/>
+      <c r="BO66" s="298"/>
+      <c r="BP66" s="298"/>
+      <c r="BQ66" s="298"/>
+      <c r="BR66" s="298"/>
+      <c r="BS66" s="298"/>
+      <c r="BT66" s="298"/>
+      <c r="BU66" s="298"/>
+      <c r="BV66" s="298"/>
+      <c r="BW66" s="298"/>
+      <c r="BX66" s="298"/>
+      <c r="BY66" s="298"/>
+      <c r="BZ66" s="298"/>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C67" s="26"/>
       <c r="D67" s="26"/>
       <c r="E67" s="26"/>
       <c r="F67" s="26"/>
-      <c r="G67" s="308"/>
-      <c r="H67" s="308"/>
-      <c r="I67" s="308"/>
-      <c r="J67" s="308"/>
+      <c r="G67" s="304"/>
+      <c r="H67" s="304"/>
+      <c r="I67" s="304"/>
+      <c r="J67" s="304"/>
       <c r="K67" s="132" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L67" s="132"/>
-      <c r="M67" s="309" t="n">
+      <c r="M67" s="305" t="n">
         <v>31</v>
       </c>
-      <c r="N67" s="309"/>
-      <c r="O67" s="309"/>
-      <c r="P67" s="309"/>
-      <c r="Q67" s="309"/>
-      <c r="R67" s="309"/>
-      <c r="S67" s="310" t="n">
+      <c r="N67" s="305"/>
+      <c r="O67" s="305"/>
+      <c r="P67" s="305"/>
+      <c r="Q67" s="305"/>
+      <c r="R67" s="305"/>
+      <c r="S67" s="306" t="n">
         <v>25</v>
       </c>
-      <c r="T67" s="310"/>
-      <c r="U67" s="310"/>
-      <c r="V67" s="310"/>
-      <c r="W67" s="310"/>
-      <c r="X67" s="310"/>
-      <c r="Y67" s="310"/>
-      <c r="Z67" s="310"/>
-      <c r="AA67" s="310"/>
-      <c r="AB67" s="311"/>
-      <c r="AC67" s="311"/>
-      <c r="AD67" s="311"/>
-      <c r="AE67" s="311"/>
+      <c r="T67" s="306"/>
+      <c r="U67" s="306"/>
+      <c r="V67" s="306"/>
+      <c r="W67" s="306"/>
+      <c r="X67" s="306"/>
+      <c r="Y67" s="306"/>
+      <c r="Z67" s="306"/>
+      <c r="AA67" s="306"/>
+      <c r="AB67" s="307"/>
+      <c r="AC67" s="307"/>
+      <c r="AD67" s="307"/>
+      <c r="AE67" s="307"/>
       <c r="AF67" s="174" t="n">
         <v>6</v>
       </c>
       <c r="AG67" s="174"/>
-      <c r="AH67" s="311"/>
-      <c r="AI67" s="311"/>
-      <c r="AJ67" s="311"/>
-      <c r="AK67" s="311"/>
-      <c r="AL67" s="312" t="n">
+      <c r="AH67" s="307"/>
+      <c r="AI67" s="307"/>
+      <c r="AJ67" s="307"/>
+      <c r="AK67" s="307"/>
+      <c r="AL67" s="308" t="n">
         <v>12</v>
       </c>
-      <c r="AM67" s="312"/>
-      <c r="AO67" s="302"/>
-      <c r="AP67" s="302"/>
-      <c r="AQ67" s="302"/>
-      <c r="AR67" s="302"/>
-      <c r="AS67" s="302"/>
-      <c r="AT67" s="302"/>
-      <c r="AU67" s="302"/>
-      <c r="AV67" s="302"/>
-      <c r="AW67" s="302"/>
-      <c r="AX67" s="302"/>
-      <c r="AY67" s="302"/>
-      <c r="AZ67" s="302"/>
-      <c r="BA67" s="302"/>
-      <c r="BB67" s="302"/>
-      <c r="BC67" s="302"/>
-      <c r="BD67" s="302"/>
-      <c r="BE67" s="302"/>
-      <c r="BF67" s="302"/>
-      <c r="BG67" s="302"/>
-      <c r="BH67" s="302"/>
-      <c r="BI67" s="302"/>
-      <c r="BJ67" s="302"/>
-      <c r="BK67" s="302"/>
-      <c r="BL67" s="302"/>
-      <c r="BM67" s="302"/>
-      <c r="BN67" s="302"/>
-      <c r="BO67" s="302"/>
-      <c r="BP67" s="302"/>
-      <c r="BQ67" s="302"/>
-      <c r="BR67" s="302"/>
-      <c r="BS67" s="302"/>
-      <c r="BT67" s="302"/>
-      <c r="BU67" s="302"/>
-      <c r="BV67" s="302"/>
-      <c r="BW67" s="302"/>
-      <c r="BX67" s="302"/>
-      <c r="BY67" s="302"/>
-      <c r="BZ67" s="302"/>
+      <c r="AM67" s="308"/>
+      <c r="AO67" s="298"/>
+      <c r="AP67" s="298"/>
+      <c r="AQ67" s="298"/>
+      <c r="AR67" s="298"/>
+      <c r="AS67" s="298"/>
+      <c r="AT67" s="298"/>
+      <c r="AU67" s="298"/>
+      <c r="AV67" s="298"/>
+      <c r="AW67" s="298"/>
+      <c r="AX67" s="298"/>
+      <c r="AY67" s="298"/>
+      <c r="AZ67" s="298"/>
+      <c r="BA67" s="298"/>
+      <c r="BB67" s="298"/>
+      <c r="BC67" s="298"/>
+      <c r="BD67" s="298"/>
+      <c r="BE67" s="298"/>
+      <c r="BF67" s="298"/>
+      <c r="BG67" s="298"/>
+      <c r="BH67" s="298"/>
+      <c r="BI67" s="298"/>
+      <c r="BJ67" s="298"/>
+      <c r="BK67" s="298"/>
+      <c r="BL67" s="298"/>
+      <c r="BM67" s="298"/>
+      <c r="BN67" s="298"/>
+      <c r="BO67" s="298"/>
+      <c r="BP67" s="298"/>
+      <c r="BQ67" s="298"/>
+      <c r="BR67" s="298"/>
+      <c r="BS67" s="298"/>
+      <c r="BT67" s="298"/>
+      <c r="BU67" s="298"/>
+      <c r="BV67" s="298"/>
+      <c r="BW67" s="298"/>
+      <c r="BX67" s="298"/>
+      <c r="BY67" s="298"/>
+      <c r="BZ67" s="298"/>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AO68" s="313" t="s">
-        <v>188</v>
-      </c>
-      <c r="AP68" s="314"/>
-      <c r="AQ68" s="314"/>
-      <c r="AR68" s="314"/>
-      <c r="AS68" s="314"/>
-      <c r="AT68" s="314"/>
-      <c r="AU68" s="314"/>
-      <c r="AV68" s="314"/>
-      <c r="AW68" s="314"/>
-      <c r="AX68" s="314"/>
-      <c r="AY68" s="314"/>
-      <c r="AZ68" s="314"/>
-      <c r="BA68" s="314"/>
-      <c r="BB68" s="314"/>
-      <c r="BC68" s="314"/>
-      <c r="BD68" s="314"/>
-      <c r="BE68" s="314"/>
-      <c r="BF68" s="314"/>
-      <c r="BG68" s="314"/>
-      <c r="BH68" s="314"/>
-      <c r="BI68" s="314"/>
-      <c r="BJ68" s="314"/>
-      <c r="BK68" s="314"/>
-      <c r="BL68" s="314"/>
-      <c r="BM68" s="314"/>
-      <c r="BN68" s="314"/>
-      <c r="BO68" s="314"/>
-      <c r="BP68" s="314"/>
-      <c r="BQ68" s="314"/>
-      <c r="BR68" s="314"/>
-      <c r="BS68" s="314"/>
-      <c r="BT68" s="314"/>
-      <c r="BU68" s="314"/>
-      <c r="BV68" s="314"/>
-      <c r="BW68" s="314"/>
-      <c r="BX68" s="314"/>
-      <c r="BY68" s="314"/>
-      <c r="BZ68" s="314"/>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AO68" s="309" t="s">
+        <v>189</v>
+      </c>
+      <c r="AP68" s="310"/>
+      <c r="AQ68" s="310"/>
+      <c r="AR68" s="310"/>
+      <c r="AS68" s="310"/>
+      <c r="AT68" s="310"/>
+      <c r="AU68" s="310"/>
+      <c r="AV68" s="310"/>
+      <c r="AW68" s="310"/>
+      <c r="AX68" s="310"/>
+      <c r="AY68" s="310"/>
+      <c r="AZ68" s="310"/>
+      <c r="BA68" s="310"/>
+      <c r="BB68" s="310"/>
+      <c r="BC68" s="310"/>
+      <c r="BD68" s="310"/>
+      <c r="BE68" s="310"/>
+      <c r="BF68" s="310"/>
+      <c r="BG68" s="310"/>
+      <c r="BH68" s="310"/>
+      <c r="BI68" s="310"/>
+      <c r="BJ68" s="310"/>
+      <c r="BK68" s="310"/>
+      <c r="BL68" s="310"/>
+      <c r="BM68" s="310"/>
+      <c r="BN68" s="310"/>
+      <c r="BO68" s="310"/>
+      <c r="BP68" s="310"/>
+      <c r="BQ68" s="310"/>
+      <c r="BR68" s="310"/>
+      <c r="BS68" s="310"/>
+      <c r="BT68" s="310"/>
+      <c r="BU68" s="310"/>
+      <c r="BV68" s="310"/>
+      <c r="BW68" s="310"/>
+      <c r="BX68" s="310"/>
+      <c r="BY68" s="310"/>
+      <c r="BZ68" s="310"/>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BZ69" s="315" t="s">
-        <v>189</v>
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="BZ69" s="311" t="s">
+        <v>190</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV70" s="206"/>
       <c r="AW70" s="206"/>
       <c r="AX70" s="206"/>
@@ -8532,7 +8517,7 @@
       <c r="BS70" s="206"/>
       <c r="BT70" s="206"/>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV71" s="206"/>
       <c r="AW71" s="206"/>
       <c r="AX71" s="206"/>
@@ -8559,7 +8544,7 @@
       <c r="BS71" s="206"/>
       <c r="BT71" s="206"/>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV72" s="206"/>
       <c r="AW72" s="206"/>
       <c r="AX72" s="206"/>
@@ -8586,7 +8571,7 @@
       <c r="BS72" s="206"/>
       <c r="BT72" s="206"/>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV73" s="206"/>
       <c r="AW73" s="206"/>
       <c r="AX73" s="206"/>
@@ -8613,12 +8598,12 @@
       <c r="BS73" s="206"/>
       <c r="BT73" s="206"/>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV74" s="206"/>
       <c r="AW74" s="206"/>
       <c r="AX74" s="206"/>
       <c r="AY74" s="206"/>
-      <c r="AZ74" s="315"/>
+      <c r="AZ74" s="311"/>
       <c r="BA74" s="206"/>
       <c r="BB74" s="206"/>
       <c r="BC74" s="206"/>
@@ -8640,7 +8625,7 @@
       <c r="BS74" s="206"/>
       <c r="BT74" s="206"/>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV75" s="206"/>
       <c r="AW75" s="206"/>
       <c r="AX75" s="206"/>
@@ -8667,7 +8652,7 @@
       <c r="BS75" s="206"/>
       <c r="BT75" s="206"/>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV76" s="206"/>
       <c r="AW76" s="206"/>
       <c r="AX76" s="206"/>
@@ -8694,7 +8679,7 @@
       <c r="BS76" s="206"/>
       <c r="BT76" s="206"/>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV77" s="206"/>
       <c r="AW77" s="206"/>
       <c r="AX77" s="206"/>
@@ -8721,7 +8706,7 @@
       <c r="BS77" s="206"/>
       <c r="BT77" s="206"/>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV78" s="206"/>
       <c r="AW78" s="206"/>
       <c r="AX78" s="206"/>
@@ -8748,7 +8733,7 @@
       <c r="BS78" s="206"/>
       <c r="BT78" s="206"/>
     </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV79" s="206"/>
       <c r="AW79" s="206"/>
       <c r="AX79" s="206"/>
@@ -8775,7 +8760,7 @@
       <c r="BS79" s="206"/>
       <c r="BT79" s="206"/>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AV80" s="206"/>
       <c r="AW80" s="206"/>
       <c r="AX80" s="206"/>

--- a/RIGEL/会社概要・資料/事業計画書・融資/日本政策金融公庫_創業計画書.xlsx
+++ b/RIGEL/会社概要・資料/事業計画書・融資/日本政策金融公庫_創業計画書.xlsx
@@ -559,7 +559,7 @@
   </si>
   <si>
     <t xml:space="preserve">【創業当初】FA設備1台/年、RTS販売3台/年、RTSレンタル2台稼働/年を前提に年商2,269万円→月平均189万円。売上原価はFA平均原価375万円/台、RTS平均原価140万円/台で試算。経費は固定費年630万円（月52.5万円）を基準に、家賃12万円・支払利息4万円・その他37万円で置いた。
-【1年後】FA設備1.5台/年、RTS販売4台/年、RTSレンタル4台稼働/年を前提に年商3,467万円→月平均289万円。※代表者報酬・自己資金額・利率は要本人確認。</t>
+【1年後】FA設備1.5台/年、RTS販売4台/年、RTSレンタル4台稼働/年を前提に年商3,467万円→月平均289万円。※代表者報酬は年500万円（月42万円、家族5人・千葉県柏市在住を踏まえた創業1年目の妥当水準として設定）を人件費に計上。</t>
   </si>
   <si>
     <t xml:space="preserve">(</t>
@@ -705,7 +705,7 @@
   <si>
     <t xml:space="preserve">最大の論点は運転資金確保。FA設備は設計〜検収〜入金まで3〜6か月を要し、先行部材費が大きい。
 初期投資848万円、運転資金2,035万円、合計2,883万円を資金計画の基準値とした。
-なお、代表者経歴、自己資金額、取引先実名、見積書、必要許認可の有無は提出前に本人確認が必要。
+代表者報酬は年500万円を計上済み。なお、取引先実名・見積書は提出前に本人確認が必要。
 自己資金300万円、日本政策金融公庫からの借入2,583万円（想定利率2.5%）で資金計画を構成。</t>
   </si>
   <si>
@@ -6607,7 +6607,7 @@
       <c r="AR46" s="236"/>
       <c r="AS46" s="236"/>
       <c r="AT46" s="237" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU46" s="237"/>
       <c r="AV46" s="237"/>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AY46" s="238"/>
       <c r="AZ46" s="237" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BA46" s="237"/>
       <c r="BB46" s="237"/>
@@ -7255,7 +7255,7 @@
       <c r="AS54" s="276"/>
       <c r="AT54" s="277" t="n">
         <f aca="false">IF(AND(AT46="",AT48="",AT50="",AT52=""),"",SUM(AT46:AW53))</f>
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="AU54" s="277"/>
       <c r="AV54" s="277"/>
@@ -7266,7 +7266,7 @@
       <c r="AY54" s="278"/>
       <c r="AZ54" s="277" t="n">
         <f aca="false">IF(AND(AZ46="",AZ48="",AZ50="",AZ52=""),"",SUM(AZ46:AZ53))</f>
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="BA54" s="277"/>
       <c r="BB54" s="277"/>
@@ -7439,7 +7439,7 @@
       <c r="AS56" s="287"/>
       <c r="AT56" s="288" t="n">
         <f aca="false">IF(AT54="","",AT41-AT44-AT54)</f>
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AU56" s="288"/>
       <c r="AV56" s="288"/>
@@ -7450,7 +7450,7 @@
       <c r="AY56" s="289"/>
       <c r="AZ56" s="288" t="n">
         <f aca="false">IF(AZ54="","",AZ41-AZ44-AZ54)</f>
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="BA56" s="288"/>
       <c r="BB56" s="288"/>
